--- a/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
   <si>
     <t>IOR</t>
   </si>
@@ -656,140 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -880,8 +887,14 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -972,8 +985,14 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1083,14 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1315,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,8 +1413,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,55 +1548,57 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
         <v>400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>500</v>
-      </c>
-      <c r="K17" s="3">
-        <v>400</v>
-      </c>
-      <c r="L17" s="3">
-        <v>300</v>
       </c>
       <c r="M17" s="3">
         <v>400</v>
       </c>
       <c r="N17" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="O17" s="3">
         <v>400</v>
       </c>
       <c r="P17" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="Q17" s="3">
         <v>400</v>
       </c>
       <c r="R17" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="S17" s="3">
         <v>400</v>
@@ -1560,37 +1613,43 @@
         <v>400</v>
       </c>
       <c r="W17" s="3">
+        <v>400</v>
+      </c>
+      <c r="X17" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y17" s="3">
         <v>500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>400</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>300</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>300</v>
       </c>
       <c r="AB17" s="3">
         <v>300</v>
       </c>
       <c r="AC17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE17" s="3">
         <v>400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1598,46 +1657,46 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G18" s="3">
         <v>-500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-300</v>
       </c>
       <c r="M18" s="3">
         <v>-400</v>
       </c>
       <c r="N18" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="O18" s="3">
         <v>-400</v>
       </c>
       <c r="P18" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="Q18" s="3">
         <v>-400</v>
       </c>
       <c r="R18" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="S18" s="3">
         <v>-400</v>
@@ -1652,37 +1711,43 @@
         <v>-400</v>
       </c>
       <c r="W18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-400</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-300</v>
       </c>
       <c r="AB18" s="3">
         <v>-300</v>
       </c>
       <c r="AC18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1780,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1724,91 +1791,97 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G20" s="3">
         <v>2800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>1800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>2100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>2000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>1700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>1600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>1600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>8500</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>1000</v>
       </c>
       <c r="AA20" s="3">
         <v>1100</v>
       </c>
       <c r="AB20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD20" s="3">
         <v>900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>1400</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>1100</v>
       </c>
       <c r="AF20" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1899,8 +1972,14 @@
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1976,135 +2055,147 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>4</v>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F23" s="3">
         <v>2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>7900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>1000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
+        <v>400</v>
+      </c>
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
-      </c>
-      <c r="H24" s="3">
-        <v>200</v>
-      </c>
-      <c r="I24" s="3">
-        <v>200</v>
       </c>
       <c r="J24" s="3">
         <v>200</v>
@@ -2119,16 +2210,16 @@
         <v>200</v>
       </c>
       <c r="N24" s="3">
+        <v>200</v>
+      </c>
+      <c r="O24" s="3">
+        <v>200</v>
+      </c>
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
-      </c>
-      <c r="P24" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>300</v>
       </c>
       <c r="R24" s="3">
         <v>200</v>
@@ -2137,7 +2228,7 @@
         <v>300</v>
       </c>
       <c r="T24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U24" s="3">
         <v>300</v>
@@ -2149,34 +2240,40 @@
         <v>300</v>
       </c>
       <c r="X24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z24" s="3">
         <v>1900</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC24" s="3">
         <v>1100</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AD24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>1100</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,49 +2364,55 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F26" s="3">
         <v>1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1400</v>
-      </c>
-      <c r="O26" s="3">
-        <v>1300</v>
-      </c>
-      <c r="P26" s="3">
-        <v>800</v>
       </c>
       <c r="Q26" s="3">
         <v>1300</v>
@@ -2318,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="S26" s="3">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="T26" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="U26" s="3">
         <v>1100</v>
@@ -2330,78 +2433,84 @@
         <v>1000</v>
       </c>
       <c r="W26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y26" s="3">
         <v>800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>6000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>1000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F27" s="3">
         <v>1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1400</v>
-      </c>
-      <c r="O27" s="3">
-        <v>1300</v>
-      </c>
-      <c r="P27" s="3">
-        <v>800</v>
       </c>
       <c r="Q27" s="3">
         <v>1300</v>
@@ -2410,10 +2519,10 @@
         <v>800</v>
       </c>
       <c r="S27" s="3">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="T27" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="U27" s="3">
         <v>1100</v>
@@ -2422,37 +2531,43 @@
         <v>1000</v>
       </c>
       <c r="W27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y27" s="3">
         <v>800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>6000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>1000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2618,14 +2739,14 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-500</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>4</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2952,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2828,132 +2967,138 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-1800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-2100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-2000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-1700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-1600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-1600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-8500</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA32" s="3">
         <v>-1100</v>
       </c>
       <c r="AB32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-1100</v>
       </c>
       <c r="AF32" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F33" s="3">
         <v>1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1400</v>
-      </c>
-      <c r="O33" s="3">
-        <v>1300</v>
-      </c>
-      <c r="P33" s="3">
-        <v>800</v>
       </c>
       <c r="Q33" s="3">
         <v>1300</v>
@@ -2962,10 +3107,10 @@
         <v>800</v>
       </c>
       <c r="S33" s="3">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="T33" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="U33" s="3">
         <v>1100</v>
@@ -2974,37 +3119,43 @@
         <v>1000</v>
       </c>
       <c r="W33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y33" s="3">
         <v>800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>6000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>1000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,49 +3246,55 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F35" s="3">
         <v>1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1400</v>
-      </c>
-      <c r="O35" s="3">
-        <v>1300</v>
-      </c>
-      <c r="P35" s="3">
-        <v>800</v>
       </c>
       <c r="Q35" s="3">
         <v>1300</v>
@@ -3146,10 +3303,10 @@
         <v>800</v>
       </c>
       <c r="S35" s="3">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="T35" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="U35" s="3">
         <v>1100</v>
@@ -3158,134 +3315,146 @@
         <v>1000</v>
       </c>
       <c r="W35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y35" s="3">
         <v>800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>6000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>1000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,8 +3523,10 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3361,7 +3534,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F41" s="3">
         <v>0</v>
@@ -3394,14 +3567,14 @@
         <v>0</v>
       </c>
       <c r="P41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3">
         <v>100</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
       <c r="S41" s="3">
         <v>0</v>
       </c>
@@ -3444,8 +3617,14 @@
       <c r="AF41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,100 +3715,112 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>107300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>106500</v>
+      </c>
+      <c r="F43" s="3">
         <v>104800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>103000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>101600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>100100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>99200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>97700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>97200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>96300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>95800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>94800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>94300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>90500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>89500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>88300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>87500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>86200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>85600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>84200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>83500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>82100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>81700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>51800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>50800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>49600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>50400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>48300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>39300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>37800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3911,14 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3812,8 +4009,14 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,19 +4107,25 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>11500</v>
+      </c>
+      <c r="F47" s="3">
         <v>11700</v>
-      </c>
-      <c r="E47" s="3">
-        <v>11800</v>
-      </c>
-      <c r="F47" s="3">
-        <v>11500</v>
       </c>
       <c r="G47" s="3">
         <v>11800</v>
@@ -3943,13 +4152,13 @@
         <v>11500</v>
       </c>
       <c r="O47" s="3">
+        <v>11800</v>
+      </c>
+      <c r="P47" s="3">
+        <v>11500</v>
+      </c>
+      <c r="Q47" s="3">
         <v>13900</v>
-      </c>
-      <c r="P47" s="3">
-        <v>13600</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>14000</v>
       </c>
       <c r="R47" s="3">
         <v>13600</v>
@@ -3985,19 +4194,25 @@
         <v>13600</v>
       </c>
       <c r="AC47" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>13600</v>
+      </c>
+      <c r="AE47" s="3">
         <v>15100</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>22900</v>
-      </c>
-      <c r="AE47" s="3">
-        <v>23700</v>
       </c>
       <c r="AF47" s="3">
         <v>22900</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>23700</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>22900</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4065,10 +4280,10 @@
         <v>0</v>
       </c>
       <c r="Y48" s="3">
-        <v>22700</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="3">
-        <v>22700</v>
+        <v>0</v>
       </c>
       <c r="AA48" s="3">
         <v>22700</v>
@@ -4088,8 +4303,14 @@
       <c r="AF48" s="3">
         <v>22700</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>22700</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>22700</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4597,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4456,8 +4695,14 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>118700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>118100</v>
+      </c>
+      <c r="F54" s="3">
         <v>116500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>114900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>113100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>112000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>110700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>109500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>108700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>108100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>107400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>106600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>105800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>104500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>103100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>102400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>101100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>100300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>99200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>98200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>97100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>96100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>95300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>89300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>88600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>87900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>88700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>88100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>87100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>86400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,19 +4967,21 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>4</v>
+      <c r="D57" s="3">
+        <v>0</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
       </c>
-      <c r="F57" s="3">
-        <v>0</v>
+      <c r="F57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G57" s="3">
         <v>0</v>
@@ -4800,8 +5061,14 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,8 +5159,14 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4984,8 +5257,14 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5076,8 +5355,14 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5168,8 +5453,14 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5260,8 +5551,14 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,8 +5845,14 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5628,8 +5943,14 @@
       <c r="AF66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>57000</v>
+      </c>
+      <c r="F72" s="3">
         <v>54600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>52900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>51100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>50000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>48800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>47600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>46700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>46100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>45400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>44700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>43900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>42500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>41200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>40400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>39100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>38300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>37200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>36200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>35100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>34100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>33300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>27300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>26600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>25900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>26800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>26200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>25200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>24400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>118700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>118100</v>
+      </c>
+      <c r="F76" s="3">
         <v>116500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>114900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>113000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>112000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>110700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>109500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>108700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>108100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>107300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>106600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>105800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>104500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>103100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>102300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>101100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>100200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>99200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>98200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>97100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>96100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>95300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>89300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>88600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>87900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>88700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>88100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>87100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>86400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,146 +6959,158 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F81" s="3">
         <v>1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1400</v>
-      </c>
-      <c r="O81" s="3">
-        <v>1300</v>
-      </c>
-      <c r="P81" s="3">
-        <v>800</v>
       </c>
       <c r="Q81" s="3">
         <v>1300</v>
@@ -6730,10 +7119,10 @@
         <v>800</v>
       </c>
       <c r="S81" s="3">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="T81" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="U81" s="3">
         <v>1100</v>
@@ -6742,37 +7131,43 @@
         <v>1000</v>
       </c>
       <c r="W81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y81" s="3">
         <v>800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>6000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>1000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,16 +7784,22 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F89" s="3">
         <v>0</v>
@@ -7384,73 +7817,79 @@
         <v>0</v>
       </c>
       <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
         <v>-8300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>3800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>9200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>1500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7575,8 +8016,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +8212,14 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7795,64 +8254,70 @@
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>3000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-1400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>9800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>1000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,31 +8738,37 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+        <v>-600</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -8345,8 +8836,14 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,8 +8934,14 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8446,7 +8949,7 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
@@ -8527,6 +9030,12 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>IOR</t>
   </si>
@@ -656,147 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -893,8 +897,11 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,8 +1576,9 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1559,49 +1586,49 @@
         <v>100</v>
       </c>
       <c r="E17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
         <v>400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>500</v>
       </c>
       <c r="H17" s="3">
         <v>500</v>
       </c>
       <c r="I17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="J17" s="3">
         <v>400</v>
       </c>
       <c r="K17" s="3">
+        <v>400</v>
+      </c>
+      <c r="L17" s="3">
         <v>300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
-      </c>
-      <c r="S17" s="3">
-        <v>400</v>
       </c>
       <c r="T17" s="3">
         <v>400</v>
@@ -1619,16 +1646,16 @@
         <v>400</v>
       </c>
       <c r="Y17" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z17" s="3">
         <v>500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>400</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>300</v>
       </c>
       <c r="AC17" s="3">
         <v>300</v>
@@ -1637,19 +1664,22 @@
         <v>300</v>
       </c>
       <c r="AE17" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AF17" s="3">
         <v>400</v>
       </c>
       <c r="AG17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AH17" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1657,49 +1687,49 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>-400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-500</v>
       </c>
       <c r="H18" s="3">
         <v>-500</v>
       </c>
       <c r="I18" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="J18" s="3">
         <v>-400</v>
       </c>
       <c r="K18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-400</v>
       </c>
       <c r="T18" s="3">
         <v>-400</v>
@@ -1717,16 +1747,16 @@
         <v>-400</v>
       </c>
       <c r="Y18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-300</v>
       </c>
       <c r="AC18" s="3">
         <v>-300</v>
@@ -1735,19 +1765,22 @@
         <v>-300</v>
       </c>
       <c r="AE18" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="AF18" s="3">
         <v>-400</v>
       </c>
       <c r="AG18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AH18" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1791,88 +1825,88 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F20" s="3">
         <v>2900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1300</v>
       </c>
       <c r="M20" s="3">
         <v>1300</v>
       </c>
       <c r="N20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O20" s="3">
         <v>1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1500</v>
-      </c>
-      <c r="U20" s="3">
-        <v>1700</v>
       </c>
       <c r="V20" s="3">
         <v>1700</v>
       </c>
       <c r="W20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X20" s="3">
         <v>1800</v>
-      </c>
-      <c r="X20" s="3">
-        <v>1600</v>
       </c>
       <c r="Y20" s="3">
         <v>1600</v>
       </c>
       <c r="Z20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AA20" s="3">
         <v>8500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1400</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>1100</v>
       </c>
       <c r="AG20" s="3">
         <v>1100</v>
@@ -1880,8 +1914,11 @@
       <c r="AH20" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1978,8 +2015,11 @@
       <c r="AH21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2061,8 +2101,8 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>4</v>
+      <c r="AD22" s="3">
+        <v>0</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>4</v>
@@ -2070,14 +2110,17 @@
       <c r="AF22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
+      <c r="AG22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2085,97 +2128,100 @@
         <v>1500</v>
       </c>
       <c r="E23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F23" s="3">
         <v>2900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>800</v>
-      </c>
-      <c r="M23" s="3">
-        <v>900</v>
       </c>
       <c r="N23" s="3">
         <v>900</v>
       </c>
       <c r="O23" s="3">
+        <v>900</v>
+      </c>
+      <c r="P23" s="3">
         <v>1000</v>
-      </c>
-      <c r="P23" s="3">
-        <v>1700</v>
       </c>
       <c r="Q23" s="3">
         <v>1700</v>
       </c>
       <c r="R23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S23" s="3">
         <v>1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1100</v>
-      </c>
-      <c r="U23" s="3">
-        <v>1300</v>
       </c>
       <c r="V23" s="3">
         <v>1300</v>
       </c>
       <c r="W23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X23" s="3">
         <v>1400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>7900</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>700</v>
       </c>
       <c r="AB23" s="3">
         <v>700</v>
       </c>
       <c r="AC23" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD23" s="3">
         <v>800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>700</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>800</v>
       </c>
       <c r="AH23" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2183,22 +2229,22 @@
         <v>300</v>
       </c>
       <c r="E24" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F24" s="3">
         <v>400</v>
       </c>
       <c r="G24" s="3">
+        <v>400</v>
+      </c>
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
-      </c>
-      <c r="J24" s="3">
-        <v>200</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
@@ -2216,22 +2262,22 @@
         <v>200</v>
       </c>
       <c r="P24" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="Q24" s="3">
         <v>400</v>
       </c>
       <c r="R24" s="3">
+        <v>400</v>
+      </c>
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
-      </c>
-      <c r="U24" s="3">
-        <v>300</v>
       </c>
       <c r="V24" s="3">
         <v>300</v>
@@ -2246,34 +2292,37 @@
         <v>300</v>
       </c>
       <c r="Z24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA24" s="3">
         <v>1900</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD24" s="3">
         <v>1100</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
+      <c r="AF24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>1100</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,8 +2419,11 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2379,97 +2431,100 @@
         <v>1200</v>
       </c>
       <c r="E26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F26" s="3">
         <v>2500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>600</v>
-      </c>
-      <c r="M26" s="3">
-        <v>700</v>
       </c>
       <c r="N26" s="3">
         <v>700</v>
       </c>
       <c r="O26" s="3">
+        <v>700</v>
+      </c>
+      <c r="P26" s="3">
         <v>800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6000</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>700</v>
       </c>
       <c r="AB26" s="3">
         <v>700</v>
       </c>
       <c r="AC26" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2477,97 +2532,100 @@
         <v>1200</v>
       </c>
       <c r="E27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F27" s="3">
         <v>2500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>600</v>
-      </c>
-      <c r="M27" s="3">
-        <v>700</v>
       </c>
       <c r="N27" s="3">
         <v>700</v>
       </c>
       <c r="O27" s="3">
+        <v>700</v>
+      </c>
+      <c r="P27" s="3">
         <v>800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6000</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>700</v>
       </c>
       <c r="AB27" s="3">
         <v>700</v>
       </c>
       <c r="AC27" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2745,11 +2806,11 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-500</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>4</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2967,88 +3037,88 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-1300</v>
       </c>
       <c r="M32" s="3">
         <v>-1300</v>
       </c>
       <c r="N32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="O32" s="3">
         <v>-1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-1700</v>
       </c>
       <c r="V32" s="3">
         <v>-1700</v>
       </c>
       <c r="W32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="X32" s="3">
         <v>-1800</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-1600</v>
       </c>
       <c r="Y32" s="3">
         <v>-1600</v>
       </c>
       <c r="Z32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-1100</v>
       </c>
       <c r="AG32" s="3">
         <v>-1100</v>
@@ -3056,8 +3126,11 @@
       <c r="AH32" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3065,97 +3138,100 @@
         <v>1200</v>
       </c>
       <c r="E33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F33" s="3">
         <v>2500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>600</v>
-      </c>
-      <c r="M33" s="3">
-        <v>700</v>
       </c>
       <c r="N33" s="3">
         <v>700</v>
       </c>
       <c r="O33" s="3">
+        <v>700</v>
+      </c>
+      <c r="P33" s="3">
         <v>800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6000</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>700</v>
       </c>
       <c r="AB33" s="3">
         <v>700</v>
       </c>
       <c r="AC33" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,8 +3328,11 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3261,200 +3340,206 @@
         <v>1200</v>
       </c>
       <c r="E35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F35" s="3">
         <v>2500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>600</v>
-      </c>
-      <c r="M35" s="3">
-        <v>700</v>
       </c>
       <c r="N35" s="3">
         <v>700</v>
       </c>
       <c r="O35" s="3">
+        <v>700</v>
+      </c>
+      <c r="P35" s="3">
         <v>800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6000</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>700</v>
       </c>
       <c r="AB35" s="3">
         <v>700</v>
       </c>
       <c r="AC35" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,8 +3611,9 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3534,11 +3621,11 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
       <c r="G41" s="3">
         <v>0</v>
       </c>
@@ -3573,11 +3660,11 @@
         <v>0</v>
       </c>
       <c r="R41" s="3">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3">
         <v>100</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
       <c r="T41" s="3">
         <v>0</v>
       </c>
@@ -3623,8 +3710,11 @@
       <c r="AH41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,106 +3811,112 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>108300</v>
+      </c>
+      <c r="E43" s="3">
         <v>107300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>106500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>104800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>103000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>101600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>100100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>99200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>97700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>97200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>96300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>95800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>94800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>94300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>90500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>89500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>88300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>87500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>86200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>85600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>84200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>83500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>82100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>81700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>51800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>50800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>49600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>50400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>48300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>39300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>37800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4015,8 +4114,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4113,106 +4215,112 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E47" s="3">
         <v>11400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>11700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>14000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>14000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>14000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>14000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>14000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>14000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>15100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>22900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>23700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4286,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="AA48" s="3">
-        <v>22700</v>
+        <v>0</v>
       </c>
       <c r="AB48" s="3">
         <v>22700</v>
@@ -4309,8 +4417,11 @@
       <c r="AH48" s="3">
         <v>22700</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>22700</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>119800</v>
+      </c>
+      <c r="E54" s="3">
         <v>118700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>118100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>116500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>114900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>113100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>112000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>110700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>109500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>108700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>108100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>107400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>106600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>105800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>104500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>103100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>102400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>101100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>100300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>99200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>98200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>97100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>96100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>95300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>89300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>88600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>87900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>88700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>88100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>87100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>86400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4980,11 +5111,11 @@
       <c r="E57" s="3">
         <v>0</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H57" s="3">
         <v>0</v>
@@ -5067,8 +5198,11 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5165,8 +5299,11 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5263,8 +5400,11 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5361,8 +5501,11 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5459,8 +5602,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,8 +6006,11 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5949,8 +6107,11 @@
       <c r="AH66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>59400</v>
+      </c>
+      <c r="E72" s="3">
         <v>58200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>57000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>54600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>52900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>51100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>50000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>48800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>47600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>46700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>46100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>45400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>44700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>43900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>42500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>41200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>40400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>39100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>38300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>37200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>36200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>35100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>34100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>33300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>27300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>26600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>25900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>26800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>26200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>25200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>24400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>119800</v>
+      </c>
+      <c r="E76" s="3">
         <v>118700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>118100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>116500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>114900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>113000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>112000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>110700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>109500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>108700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>108100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>107300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>106600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>105800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>104500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>103100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>102300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>101100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>100200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>99200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>98200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>97100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>96100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>95300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>89300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>88600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>87900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>88700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>88100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>87100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>86400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,111 +7154,117 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7077,97 +7272,100 @@
         <v>1200</v>
       </c>
       <c r="E81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F81" s="3">
         <v>2500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>600</v>
-      </c>
-      <c r="M81" s="3">
-        <v>700</v>
       </c>
       <c r="N81" s="3">
         <v>700</v>
       </c>
       <c r="O81" s="3">
+        <v>700</v>
+      </c>
+      <c r="P81" s="3">
         <v>800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6000</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>700</v>
       </c>
       <c r="AB81" s="3">
         <v>700</v>
       </c>
       <c r="AC81" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,20 +8004,23 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1000</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
         <v>0</v>
       </c>
@@ -7823,73 +8040,76 @@
         <v>0</v>
       </c>
       <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>-8300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>9200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8260,64 +8490,67 @@
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>3000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>9800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>1000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,17 +8987,20 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F100" s="3" t="s">
         <v>4</v>
       </c>
@@ -8770,8 +9016,8 @@
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -8842,8 +9088,11 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,8 +9189,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8949,11 +9201,11 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
@@ -9036,6 +9288,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
   <si>
     <t>IOR</t>
   </si>
@@ -656,174 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -900,8 +904,11 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1001,8 +1008,11 @@
       <c r="AI9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,31 +1358,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1442,8 +1462,11 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,8 +1603,9 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1589,49 +1616,49 @@
         <v>100</v>
       </c>
       <c r="F17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
         <v>400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>500</v>
       </c>
       <c r="I17" s="3">
         <v>500</v>
       </c>
       <c r="J17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K17" s="3">
         <v>400</v>
       </c>
       <c r="L17" s="3">
+        <v>400</v>
+      </c>
+      <c r="M17" s="3">
         <v>300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
-      </c>
-      <c r="T17" s="3">
-        <v>400</v>
       </c>
       <c r="U17" s="3">
         <v>400</v>
@@ -1649,16 +1676,16 @@
         <v>400</v>
       </c>
       <c r="Z17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA17" s="3">
         <v>500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>400</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>300</v>
       </c>
       <c r="AD17" s="3">
         <v>300</v>
@@ -1667,72 +1694,75 @@
         <v>300</v>
       </c>
       <c r="AF17" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AG17" s="3">
         <v>400</v>
       </c>
       <c r="AH17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AI17" s="3">
         <v>300</v>
       </c>
+      <c r="AJ17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-100</v>
       </c>
       <c r="E18" s="3">
         <v>-100</v>
       </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>-400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-500</v>
       </c>
       <c r="I18" s="3">
         <v>-500</v>
       </c>
       <c r="J18" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="K18" s="3">
         <v>-400</v>
       </c>
       <c r="L18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M18" s="3">
         <v>-300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-300</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-400</v>
       </c>
       <c r="U18" s="3">
         <v>-400</v>
@@ -1750,16 +1780,16 @@
         <v>-400</v>
       </c>
       <c r="Z18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-400</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-300</v>
       </c>
       <c r="AD18" s="3">
         <v>-300</v>
@@ -1768,19 +1798,22 @@
         <v>-300</v>
       </c>
       <c r="AF18" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="AG18" s="3">
         <v>-400</v>
       </c>
       <c r="AH18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AI18" s="3">
         <v>-300</v>
       </c>
+      <c r="AJ18" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,100 +1849,101 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G20" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H20" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1400</v>
-      </c>
-      <c r="M20" s="3">
-        <v>1300</v>
       </c>
       <c r="N20" s="3">
         <v>1300</v>
       </c>
       <c r="O20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1500</v>
-      </c>
-      <c r="V20" s="3">
-        <v>1700</v>
       </c>
       <c r="W20" s="3">
         <v>1700</v>
       </c>
       <c r="X20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y20" s="3">
         <v>1800</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>1600</v>
       </c>
       <c r="Z20" s="3">
         <v>1600</v>
       </c>
       <c r="AA20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AB20" s="3">
         <v>8500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1400</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>1100</v>
       </c>
       <c r="AH20" s="3">
         <v>1100</v>
@@ -1917,31 +1951,34 @@
       <c r="AI20" s="3">
         <v>1100</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>1100</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -2018,31 +2055,34 @@
       <c r="AI21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2104,8 +2144,8 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>4</v>
+      <c r="AE22" s="3">
+        <v>0</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>4</v>
@@ -2113,14 +2153,17 @@
       <c r="AG22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH22" s="3">
-        <v>0</v>
+      <c r="AH22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2131,97 +2174,100 @@
         <v>1500</v>
       </c>
       <c r="F23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G23" s="3">
         <v>2900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>800</v>
-      </c>
-      <c r="N23" s="3">
-        <v>900</v>
       </c>
       <c r="O23" s="3">
         <v>900</v>
       </c>
       <c r="P23" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q23" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>1700</v>
       </c>
       <c r="R23" s="3">
         <v>1700</v>
       </c>
       <c r="S23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T23" s="3">
         <v>1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1100</v>
-      </c>
-      <c r="V23" s="3">
-        <v>1300</v>
       </c>
       <c r="W23" s="3">
         <v>1300</v>
       </c>
       <c r="X23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Y23" s="3">
         <v>1400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>7900</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>700</v>
       </c>
       <c r="AC23" s="3">
         <v>700</v>
       </c>
       <c r="AD23" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE23" s="3">
         <v>800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>700</v>
-      </c>
-      <c r="AH23" s="3">
-        <v>800</v>
       </c>
       <c r="AI23" s="3">
         <v>800</v>
       </c>
+      <c r="AJ23" s="3">
+        <v>800</v>
+      </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2232,22 +2278,22 @@
         <v>300</v>
       </c>
       <c r="F24" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G24" s="3">
         <v>400</v>
       </c>
       <c r="H24" s="3">
+        <v>400</v>
+      </c>
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
-      </c>
-      <c r="K24" s="3">
-        <v>200</v>
       </c>
       <c r="L24" s="3">
         <v>200</v>
@@ -2265,22 +2311,22 @@
         <v>200</v>
       </c>
       <c r="Q24" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="R24" s="3">
         <v>400</v>
       </c>
       <c r="S24" s="3">
+        <v>400</v>
+      </c>
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
-      </c>
-      <c r="V24" s="3">
-        <v>300</v>
       </c>
       <c r="W24" s="3">
         <v>300</v>
@@ -2295,34 +2341,37 @@
         <v>300</v>
       </c>
       <c r="AA24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB24" s="3">
         <v>1900</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AD24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE24" s="3">
         <v>1100</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
+      <c r="AG24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>1100</v>
       </c>
-      <c r="AI24" s="3" t="s">
+      <c r="AJ24" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,8 +2471,11 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2434,97 +2486,100 @@
         <v>1200</v>
       </c>
       <c r="F26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G26" s="3">
         <v>2500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>600</v>
-      </c>
-      <c r="N26" s="3">
-        <v>700</v>
       </c>
       <c r="O26" s="3">
         <v>700</v>
       </c>
       <c r="P26" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q26" s="3">
         <v>800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6000</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>700</v>
       </c>
       <c r="AC26" s="3">
         <v>700</v>
       </c>
       <c r="AD26" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2535,97 +2590,100 @@
         <v>1200</v>
       </c>
       <c r="F27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G27" s="3">
         <v>2500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>600</v>
-      </c>
-      <c r="N27" s="3">
-        <v>700</v>
       </c>
       <c r="O27" s="3">
         <v>700</v>
       </c>
       <c r="P27" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q27" s="3">
         <v>800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6000</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>700</v>
       </c>
       <c r="AC27" s="3">
         <v>700</v>
       </c>
       <c r="AD27" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2809,11 +2870,11 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-500</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>4</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,100 +3095,103 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-1300</v>
       </c>
       <c r="N32" s="3">
         <v>-1300</v>
       </c>
       <c r="O32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-1700</v>
       </c>
       <c r="W32" s="3">
         <v>-1700</v>
       </c>
       <c r="X32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-1600</v>
       </c>
       <c r="Z32" s="3">
         <v>-1600</v>
       </c>
       <c r="AA32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-1100</v>
       </c>
       <c r="AH32" s="3">
         <v>-1100</v>
@@ -3129,8 +3199,11 @@
       <c r="AI32" s="3">
         <v>-1100</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>-1100</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3141,97 +3214,100 @@
         <v>1200</v>
       </c>
       <c r="F33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G33" s="3">
         <v>2500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>600</v>
-      </c>
-      <c r="N33" s="3">
-        <v>700</v>
       </c>
       <c r="O33" s="3">
         <v>700</v>
       </c>
       <c r="P33" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q33" s="3">
         <v>800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6000</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>700</v>
       </c>
       <c r="AC33" s="3">
         <v>700</v>
       </c>
       <c r="AD33" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,8 +3407,11 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3343,203 +3422,209 @@
         <v>1200</v>
       </c>
       <c r="F35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G35" s="3">
         <v>2500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>600</v>
-      </c>
-      <c r="N35" s="3">
-        <v>700</v>
       </c>
       <c r="O35" s="3">
         <v>700</v>
       </c>
       <c r="P35" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q35" s="3">
         <v>800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6000</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>700</v>
       </c>
       <c r="AC35" s="3">
         <v>700</v>
       </c>
       <c r="AD35" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,8 +3698,9 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3624,11 +3711,11 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
         <v>0</v>
       </c>
@@ -3663,11 +3750,11 @@
         <v>0</v>
       </c>
       <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3">
         <v>100</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
       <c r="U41" s="3">
         <v>0</v>
       </c>
@@ -3713,8 +3800,11 @@
       <c r="AI41" s="3">
         <v>0</v>
       </c>
+      <c r="AJ41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,132 +3904,138 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>108300</v>
+        <v>109700</v>
       </c>
       <c r="E43" s="3">
-        <v>107300</v>
+        <v>108600</v>
       </c>
       <c r="F43" s="3">
-        <v>106500</v>
+        <v>107500</v>
       </c>
       <c r="G43" s="3">
-        <v>104800</v>
+        <v>106800</v>
       </c>
       <c r="H43" s="3">
-        <v>103000</v>
+        <v>105300</v>
       </c>
       <c r="I43" s="3">
-        <v>101600</v>
+        <v>103700</v>
       </c>
       <c r="J43" s="3">
+        <v>101900</v>
+      </c>
+      <c r="K43" s="3">
         <v>100100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>99200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>97700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>97200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>96300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>95800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>94800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>94300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>90500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>89500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>88300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>87500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>86200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>85600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>84200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>83500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>82100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>81700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>51800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>50800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>49600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>50400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>48300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>39300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>37800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,31 +4112,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4117,31 +4216,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>109700</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>108700</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>107500</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>106900</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>105300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>103700</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>101900</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4218,132 +4320,138 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
+        <v>11800</v>
+      </c>
+      <c r="L47" s="3">
         <v>11500</v>
       </c>
-      <c r="E47" s="3">
-        <v>11400</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="M47" s="3">
+        <v>11800</v>
+      </c>
+      <c r="N47" s="3">
         <v>11500</v>
       </c>
-      <c r="G47" s="3">
-        <v>11700</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="O47" s="3">
         <v>11800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="P47" s="3">
         <v>11500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="Q47" s="3">
         <v>11800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="R47" s="3">
         <v>11500</v>
       </c>
-      <c r="L47" s="3">
-        <v>11800</v>
-      </c>
-      <c r="M47" s="3">
-        <v>11500</v>
-      </c>
-      <c r="N47" s="3">
-        <v>11800</v>
-      </c>
-      <c r="O47" s="3">
-        <v>11500</v>
-      </c>
-      <c r="P47" s="3">
-        <v>11800</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>11500</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>14000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>14000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>14000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>14000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>14000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>14000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>15100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>22900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>23700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -4397,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="AB48" s="3">
-        <v>22700</v>
+        <v>0</v>
       </c>
       <c r="AC48" s="3">
         <v>22700</v>
@@ -4420,8 +4528,11 @@
       <c r="AI48" s="3">
         <v>22700</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>22700</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,31 +4840,34 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>120800</v>
+      </c>
+      <c r="E54" s="3">
         <v>119800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>118700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>118100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>116500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>114900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>113100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>112000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>110700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>109500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>108700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>108100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>107400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>106600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>105800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>104500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>103100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>102400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>101100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>100300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>99200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>98200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>97100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>96100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>95300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>89300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>88600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>87900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>88700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>88100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>87100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>86400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,16 +5230,17 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
         <v>0</v>
       </c>
-      <c r="E57" s="3">
-        <v>0</v>
+      <c r="E57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F57" s="3">
         <v>0</v>
@@ -5201,8 +5332,11 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5302,31 +5436,34 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -5403,22 +5540,25 @@
       <c r="AI59" s="3">
         <v>0</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
         <v>0</v>
       </c>
-      <c r="E60" s="3">
-        <v>0</v>
+      <c r="E60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F60" s="3">
         <v>0</v>
       </c>
-      <c r="G60" s="3">
-        <v>0</v>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H60" s="3">
         <v>0</v>
@@ -5504,8 +5644,11 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5605,31 +5748,34 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,22 +6164,25 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
         <v>0</v>
       </c>
-      <c r="E66" s="3">
-        <v>0</v>
+      <c r="E66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F66" s="3">
         <v>0</v>
       </c>
-      <c r="G66" s="3">
-        <v>0</v>
+      <c r="G66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H66" s="3">
         <v>0</v>
@@ -6110,8 +6268,11 @@
       <c r="AI66" s="3">
         <v>0</v>
       </c>
+      <c r="AJ66" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E72" s="3">
         <v>59400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>58200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>57000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>54600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>52900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>51100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>50000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>48800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>47600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>46700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>46100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>45400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>44700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>43900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>42500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>41200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>40400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>39100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>38300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>37200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>36200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>35100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>34100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>33300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>27300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>26600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>25900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>26800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>26200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>25200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>24400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>120800</v>
+      </c>
+      <c r="E76" s="3">
         <v>119800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>118700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>118100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>116500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>114900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>113000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>112000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>110700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>109500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>108700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>108100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>107300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>106600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>105800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>104500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>103100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>102300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>101100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>100200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>99200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>98200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>97100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>96100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>95300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>89300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>88600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>87900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>88700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>88100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>87100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>86400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,114 +7346,120 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7275,97 +7470,100 @@
         <v>1200</v>
       </c>
       <c r="F81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G81" s="3">
         <v>2500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>600</v>
-      </c>
-      <c r="N81" s="3">
-        <v>700</v>
       </c>
       <c r="O81" s="3">
         <v>700</v>
       </c>
       <c r="P81" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q81" s="3">
         <v>800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6000</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>700</v>
       </c>
       <c r="AC81" s="3">
         <v>700</v>
       </c>
       <c r="AD81" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,31 +7599,32 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,23 +8221,26 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1000</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
         <v>0</v>
       </c>
@@ -8043,73 +8260,76 @@
         <v>0</v>
       </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>-8300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-9800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>9200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,31 +8365,32 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8246,8 +8467,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,31 +8675,34 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
         <v>0</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -8493,64 +8723,67 @@
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>3000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>9800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,22 +9233,25 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-600</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>4</v>
+      <c r="G100" s="3">
+        <v>-900</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>4</v>
@@ -9019,8 +9265,8 @@
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -9091,31 +9337,34 @@
       <c r="AI100" s="3">
         <v>0</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,8 +9441,11 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9204,11 +9456,11 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
@@ -9291,6 +9543,9 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
   <si>
     <t>IOR</t>
   </si>
@@ -656,155 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -829,8 +832,8 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -907,8 +910,11 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1011,8 +1017,11 @@
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1115,8 +1124,11 @@
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1387,8 +1406,8 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1465,8 +1484,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,8 +1629,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1619,49 +1645,49 @@
         <v>100</v>
       </c>
       <c r="G17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
         <v>400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>500</v>
       </c>
       <c r="J17" s="3">
         <v>500</v>
       </c>
       <c r="K17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L17" s="3">
         <v>400</v>
       </c>
       <c r="M17" s="3">
+        <v>400</v>
+      </c>
+      <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>300</v>
-      </c>
-      <c r="U17" s="3">
-        <v>400</v>
       </c>
       <c r="V17" s="3">
         <v>400</v>
@@ -1679,16 +1705,16 @@
         <v>400</v>
       </c>
       <c r="AA17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB17" s="3">
         <v>500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>400</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>300</v>
       </c>
       <c r="AE17" s="3">
         <v>300</v>
@@ -1697,19 +1723,22 @@
         <v>300</v>
       </c>
       <c r="AG17" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AH17" s="3">
         <v>400</v>
       </c>
       <c r="AI17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AJ17" s="3">
         <v>300</v>
       </c>
+      <c r="AK17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1723,49 +1752,49 @@
         <v>-100</v>
       </c>
       <c r="G18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>-400</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-500</v>
       </c>
       <c r="J18" s="3">
         <v>-500</v>
       </c>
       <c r="K18" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="L18" s="3">
         <v>-400</v>
       </c>
       <c r="M18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-300</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-400</v>
       </c>
       <c r="V18" s="3">
         <v>-400</v>
@@ -1783,16 +1812,16 @@
         <v>-400</v>
       </c>
       <c r="AA18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-400</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-300</v>
       </c>
       <c r="AE18" s="3">
         <v>-300</v>
@@ -1801,19 +1830,22 @@
         <v>-300</v>
       </c>
       <c r="AG18" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="AH18" s="3">
         <v>-400</v>
       </c>
       <c r="AI18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AJ18" s="3">
         <v>-300</v>
       </c>
+      <c r="AK18" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1876,77 +1909,77 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1300</v>
       </c>
       <c r="O20" s="3">
         <v>1300</v>
       </c>
       <c r="P20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1500</v>
-      </c>
-      <c r="W20" s="3">
-        <v>1700</v>
       </c>
       <c r="X20" s="3">
         <v>1700</v>
       </c>
       <c r="Y20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Z20" s="3">
         <v>1800</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>1600</v>
       </c>
       <c r="AA20" s="3">
         <v>1600</v>
       </c>
       <c r="AB20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AC20" s="3">
         <v>8500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1400</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>1100</v>
       </c>
       <c r="AI20" s="3">
         <v>1100</v>
@@ -1954,8 +1987,11 @@
       <c r="AJ20" s="3">
         <v>1100</v>
       </c>
+      <c r="AK20" s="3">
+        <v>1100</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1969,19 +2005,19 @@
         <v>-100</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>-400</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-500</v>
       </c>
       <c r="J21" s="3">
         <v>-500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
+      <c r="K21" s="3">
+        <v>-500</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
@@ -2058,8 +2094,11 @@
       <c r="AJ21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2084,8 +2123,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2147,8 +2186,8 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>4</v>
+      <c r="AF22" s="3">
+        <v>0</v>
       </c>
       <c r="AG22" s="3" t="s">
         <v>4</v>
@@ -2156,19 +2195,22 @@
       <c r="AH22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI22" s="3">
-        <v>0</v>
+      <c r="AI22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="E23" s="3">
         <v>1500</v>
@@ -2177,97 +2219,100 @@
         <v>1500</v>
       </c>
       <c r="G23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H23" s="3">
         <v>2900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>800</v>
-      </c>
-      <c r="O23" s="3">
-        <v>900</v>
       </c>
       <c r="P23" s="3">
         <v>900</v>
       </c>
       <c r="Q23" s="3">
+        <v>900</v>
+      </c>
+      <c r="R23" s="3">
         <v>1000</v>
-      </c>
-      <c r="R23" s="3">
-        <v>1700</v>
       </c>
       <c r="S23" s="3">
         <v>1700</v>
       </c>
       <c r="T23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U23" s="3">
         <v>1000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1100</v>
-      </c>
-      <c r="W23" s="3">
-        <v>1300</v>
       </c>
       <c r="X23" s="3">
         <v>1300</v>
       </c>
       <c r="Y23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Z23" s="3">
         <v>1400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>7900</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>700</v>
       </c>
       <c r="AD23" s="3">
         <v>700</v>
       </c>
       <c r="AE23" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF23" s="3">
         <v>800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>700</v>
-      </c>
-      <c r="AI23" s="3">
-        <v>800</v>
       </c>
       <c r="AJ23" s="3">
         <v>800</v>
       </c>
+      <c r="AK23" s="3">
+        <v>800</v>
+      </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2281,22 +2326,22 @@
         <v>300</v>
       </c>
       <c r="G24" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H24" s="3">
         <v>400</v>
       </c>
       <c r="I24" s="3">
+        <v>400</v>
+      </c>
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
-      </c>
-      <c r="L24" s="3">
-        <v>200</v>
       </c>
       <c r="M24" s="3">
         <v>200</v>
@@ -2314,22 +2359,22 @@
         <v>200</v>
       </c>
       <c r="R24" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="S24" s="3">
         <v>400</v>
       </c>
       <c r="T24" s="3">
+        <v>400</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
-      </c>
-      <c r="W24" s="3">
-        <v>300</v>
       </c>
       <c r="X24" s="3">
         <v>300</v>
@@ -2344,34 +2389,37 @@
         <v>300</v>
       </c>
       <c r="AB24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC24" s="3">
         <v>1900</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF24" s="3">
         <v>1100</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
+      <c r="AH24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ24" s="3" t="s">
+      <c r="AK24" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,13 +2522,16 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E26" s="3">
         <v>1200</v>
@@ -2489,102 +2540,105 @@
         <v>1200</v>
       </c>
       <c r="G26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H26" s="3">
         <v>2500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>600</v>
-      </c>
-      <c r="O26" s="3">
-        <v>700</v>
       </c>
       <c r="P26" s="3">
         <v>700</v>
       </c>
       <c r="Q26" s="3">
+        <v>700</v>
+      </c>
+      <c r="R26" s="3">
         <v>800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6000</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>700</v>
       </c>
       <c r="AD26" s="3">
         <v>700</v>
       </c>
       <c r="AE26" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E27" s="3">
         <v>1200</v>
@@ -2593,97 +2647,100 @@
         <v>1200</v>
       </c>
       <c r="G27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H27" s="3">
         <v>2500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>600</v>
-      </c>
-      <c r="O27" s="3">
-        <v>700</v>
       </c>
       <c r="P27" s="3">
         <v>700</v>
       </c>
       <c r="Q27" s="3">
+        <v>700</v>
+      </c>
+      <c r="R27" s="3">
         <v>800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6000</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>700</v>
       </c>
       <c r="AD27" s="3">
         <v>700</v>
       </c>
       <c r="AE27" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2873,11 +2933,11 @@
         <v>0</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-500</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>4</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3124,77 +3193,77 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>-2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-1300</v>
       </c>
       <c r="O32" s="3">
         <v>-1300</v>
       </c>
       <c r="P32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-1700</v>
       </c>
       <c r="X32" s="3">
         <v>-1700</v>
       </c>
       <c r="Y32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-1600</v>
       </c>
       <c r="AA32" s="3">
         <v>-1600</v>
       </c>
       <c r="AB32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-1100</v>
       </c>
       <c r="AI32" s="3">
         <v>-1100</v>
@@ -3202,13 +3271,16 @@
       <c r="AJ32" s="3">
         <v>-1100</v>
       </c>
+      <c r="AK32" s="3">
+        <v>-1100</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E33" s="3">
         <v>1200</v>
@@ -3217,97 +3289,100 @@
         <v>1200</v>
       </c>
       <c r="G33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H33" s="3">
         <v>2500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>600</v>
-      </c>
-      <c r="O33" s="3">
-        <v>700</v>
       </c>
       <c r="P33" s="3">
         <v>700</v>
       </c>
       <c r="Q33" s="3">
+        <v>700</v>
+      </c>
+      <c r="R33" s="3">
         <v>800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6000</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>700</v>
       </c>
       <c r="AD33" s="3">
         <v>700</v>
       </c>
       <c r="AE33" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,13 +3485,16 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E35" s="3">
         <v>1200</v>
@@ -3425,206 +3503,212 @@
         <v>1200</v>
       </c>
       <c r="G35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H35" s="3">
         <v>2500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>600</v>
-      </c>
-      <c r="O35" s="3">
-        <v>700</v>
       </c>
       <c r="P35" s="3">
         <v>700</v>
       </c>
       <c r="Q35" s="3">
+        <v>700</v>
+      </c>
+      <c r="R35" s="3">
         <v>800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6000</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>700</v>
       </c>
       <c r="AD35" s="3">
         <v>700</v>
       </c>
       <c r="AE35" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,8 +3784,9 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3714,11 +3800,11 @@
         <v>0</v>
       </c>
       <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
       <c r="I41" s="3">
         <v>0</v>
       </c>
@@ -3753,11 +3839,11 @@
         <v>0</v>
       </c>
       <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
         <v>100</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
       <c r="V41" s="3">
         <v>0</v>
       </c>
@@ -3803,8 +3889,11 @@
       <c r="AJ41" s="3">
         <v>0</v>
       </c>
+      <c r="AK41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,112 +3996,118 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>110800</v>
+      </c>
+      <c r="E43" s="3">
         <v>109700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>108600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>107500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>106800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>105300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>103700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>101900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>100100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>99200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>97700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>97200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>96300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>95800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>94800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>94300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>90500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>89500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>88300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>87500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>86200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>85600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>84200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>83500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>82100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>81700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>51800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>50800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>49600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>50400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>48300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>39300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>37800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,8 +4210,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4141,8 +4239,8 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -4219,35 +4317,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>110800</v>
+      </c>
+      <c r="E46" s="3">
         <v>109700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>108700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>107500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>106900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>105300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>103700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>101900</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4323,8 +4424,11 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4349,86 +4453,89 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3">
         <v>11800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>14000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>14000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>14000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>14000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>14000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>14000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>13600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>15100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>22900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4453,8 +4560,8 @@
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -4508,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="AC48" s="3">
-        <v>22700</v>
+        <v>0</v>
       </c>
       <c r="AD48" s="3">
         <v>22700</v>
@@ -4531,8 +4638,11 @@
       <c r="AJ48" s="3">
         <v>22700</v>
       </c>
+      <c r="AK48" s="3">
+        <v>22700</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +4959,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4869,8 +4988,8 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4947,8 +5066,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>121900</v>
+      </c>
+      <c r="E54" s="3">
         <v>120800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>119800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>118700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>118100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>116500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>114900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>113100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>112000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>110700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>109500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>108700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>108100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>107400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>106600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>105800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>104500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>103100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>102400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>101100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>100300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>99200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>98200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>97100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>96100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>95300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>89300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>88600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>87900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>88700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>88100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>87100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>86400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,25 +5360,26 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I57" s="3">
         <v>0</v>
@@ -5335,8 +5465,11 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5439,8 +5572,11 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5465,8 +5601,8 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -5543,25 +5679,28 @@
       <c r="AJ59" s="3">
         <v>0</v>
       </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>0</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F60" s="3">
-        <v>0</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H60" s="3">
-        <v>0</v>
+      <c r="D60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E60" s="3">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" s="3">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I60" s="3">
         <v>0</v>
@@ -5647,8 +5786,11 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5751,8 +5893,11 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5777,8 +5922,8 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -5855,8 +6000,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,25 +6321,28 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>0</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F66" s="3">
-        <v>0</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H66" s="3">
-        <v>0</v>
+      <c r="D66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="3">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G66" s="3">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I66" s="3">
         <v>0</v>
@@ -6271,8 +6428,11 @@
       <c r="AJ66" s="3">
         <v>0</v>
       </c>
+      <c r="AK66" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>61700</v>
+      </c>
+      <c r="E72" s="3">
         <v>60600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>59400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>58200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>57000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>54600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>52900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>51100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>50000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>48800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>47600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>46700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>46100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>45400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>44700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>43900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>42500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>41200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>40400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>39100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>38300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>37200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>36200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>35100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>34100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>33300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>27300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>26600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>25900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>26800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>26200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>25200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>24400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>121900</v>
+      </c>
+      <c r="E76" s="3">
         <v>120800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>119800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>118700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>118100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>116500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>114900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>113000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>112000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>110700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>109500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>108700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>108100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>107300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>106600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>105800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>104500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>103100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>102300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>101100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>100200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>99200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>98200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>97100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>96100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>95300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>89300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>88600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>87900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>88700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>88100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>87100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>86400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,122 +7537,128 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E81" s="3">
         <v>1200</v>
@@ -7473,97 +7667,100 @@
         <v>1200</v>
       </c>
       <c r="G81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H81" s="3">
         <v>2500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>600</v>
-      </c>
-      <c r="O81" s="3">
-        <v>700</v>
       </c>
       <c r="P81" s="3">
         <v>700</v>
       </c>
       <c r="Q81" s="3">
+        <v>700</v>
+      </c>
+      <c r="R81" s="3">
         <v>800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6000</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>700</v>
       </c>
       <c r="AD81" s="3">
         <v>700</v>
       </c>
       <c r="AE81" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,8 +7797,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7626,8 +7824,8 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -7704,8 +7902,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,26 +8437,29 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>200</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1000</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
       <c r="I89" s="3">
         <v>0</v>
       </c>
@@ -8263,73 +8479,76 @@
         <v>0</v>
       </c>
       <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>-8300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-9800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>9200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,8 +8585,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8392,8 +8612,8 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8470,8 +8690,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,16 +8904,19 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
         <v>0</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
+      <c r="E94" s="3">
+        <v>0</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>4</v>
@@ -8704,8 +8933,8 @@
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -8726,64 +8955,67 @@
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>3000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>9800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,26 +9478,29 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-900</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>4</v>
       </c>
@@ -9268,8 +9513,8 @@
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -9340,8 +9585,11 @@
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9444,8 +9692,11 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9459,11 +9710,11 @@
         <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
@@ -9546,6 +9797,9 @@
         <v>0</v>
       </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
   <si>
     <t>IOR</t>
   </si>
@@ -656,158 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -835,8 +839,8 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -913,8 +917,11 @@
       <c r="AK8" s="3">
         <v>0</v>
       </c>
+      <c r="AL8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1020,8 +1027,11 @@
       <c r="AK9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1127,8 +1137,11 @@
       <c r="AK10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1409,8 +1429,8 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1487,8 +1507,11 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,8 +1656,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1648,49 +1675,49 @@
         <v>100</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
         <v>400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>500</v>
       </c>
       <c r="K17" s="3">
         <v>500</v>
       </c>
       <c r="L17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M17" s="3">
         <v>400</v>
       </c>
       <c r="N17" s="3">
+        <v>400</v>
+      </c>
+      <c r="O17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>300</v>
-      </c>
-      <c r="V17" s="3">
-        <v>400</v>
       </c>
       <c r="W17" s="3">
         <v>400</v>
@@ -1708,16 +1735,16 @@
         <v>400</v>
       </c>
       <c r="AB17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC17" s="3">
         <v>500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>400</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>300</v>
       </c>
       <c r="AF17" s="3">
         <v>300</v>
@@ -1726,19 +1753,22 @@
         <v>300</v>
       </c>
       <c r="AH17" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AI17" s="3">
         <v>400</v>
       </c>
       <c r="AJ17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AK17" s="3">
         <v>300</v>
       </c>
+      <c r="AL17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1755,49 +1785,49 @@
         <v>-100</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>-400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-500</v>
       </c>
       <c r="K18" s="3">
         <v>-500</v>
       </c>
       <c r="L18" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="M18" s="3">
         <v>-400</v>
       </c>
       <c r="N18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-300</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-400</v>
       </c>
       <c r="W18" s="3">
         <v>-400</v>
@@ -1815,16 +1845,16 @@
         <v>-400</v>
       </c>
       <c r="AB18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-400</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>-300</v>
       </c>
       <c r="AF18" s="3">
         <v>-300</v>
@@ -1833,19 +1863,22 @@
         <v>-300</v>
       </c>
       <c r="AH18" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="AI18" s="3">
         <v>-400</v>
       </c>
       <c r="AJ18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AK18" s="3">
         <v>-300</v>
       </c>
+      <c r="AL18" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1912,77 +1946,77 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1400</v>
-      </c>
-      <c r="O20" s="3">
-        <v>1300</v>
       </c>
       <c r="P20" s="3">
         <v>1300</v>
       </c>
       <c r="Q20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R20" s="3">
         <v>1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1500</v>
-      </c>
-      <c r="X20" s="3">
-        <v>1700</v>
       </c>
       <c r="Y20" s="3">
         <v>1700</v>
       </c>
       <c r="Z20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AA20" s="3">
         <v>1800</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>1600</v>
       </c>
       <c r="AB20" s="3">
         <v>1600</v>
       </c>
       <c r="AC20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AD20" s="3">
         <v>8500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1400</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>1100</v>
       </c>
       <c r="AJ20" s="3">
         <v>1100</v>
@@ -1990,8 +2024,11 @@
       <c r="AK20" s="3">
         <v>1100</v>
       </c>
+      <c r="AL20" s="3">
+        <v>1100</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2008,19 +2045,19 @@
         <v>-100</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>-400</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-500</v>
       </c>
       <c r="K21" s="3">
         <v>-500</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
+      <c r="L21" s="3">
+        <v>-500</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
@@ -2097,8 +2134,11 @@
       <c r="AK21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2126,8 +2166,8 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2189,8 +2229,8 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>4</v>
+      <c r="AG22" s="3">
+        <v>0</v>
       </c>
       <c r="AH22" s="3" t="s">
         <v>4</v>
@@ -2198,22 +2238,25 @@
       <c r="AI22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ22" s="3">
-        <v>0</v>
+      <c r="AJ22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E23" s="3">
         <v>1400</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1500</v>
       </c>
       <c r="F23" s="3">
         <v>1500</v>
@@ -2222,97 +2265,100 @@
         <v>1500</v>
       </c>
       <c r="H23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I23" s="3">
         <v>2900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>800</v>
-      </c>
-      <c r="P23" s="3">
-        <v>900</v>
       </c>
       <c r="Q23" s="3">
         <v>900</v>
       </c>
       <c r="R23" s="3">
+        <v>900</v>
+      </c>
+      <c r="S23" s="3">
         <v>1000</v>
-      </c>
-      <c r="S23" s="3">
-        <v>1700</v>
       </c>
       <c r="T23" s="3">
         <v>1700</v>
       </c>
       <c r="U23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V23" s="3">
         <v>1000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1100</v>
-      </c>
-      <c r="X23" s="3">
-        <v>1300</v>
       </c>
       <c r="Y23" s="3">
         <v>1300</v>
       </c>
       <c r="Z23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA23" s="3">
         <v>1400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>7900</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>700</v>
       </c>
       <c r="AE23" s="3">
         <v>700</v>
       </c>
       <c r="AF23" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG23" s="3">
         <v>800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>700</v>
-      </c>
-      <c r="AJ23" s="3">
-        <v>800</v>
       </c>
       <c r="AK23" s="3">
         <v>800</v>
       </c>
+      <c r="AL23" s="3">
+        <v>800</v>
+      </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2329,22 +2375,22 @@
         <v>300</v>
       </c>
       <c r="H24" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I24" s="3">
         <v>400</v>
       </c>
       <c r="J24" s="3">
+        <v>400</v>
+      </c>
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
-      </c>
-      <c r="M24" s="3">
-        <v>200</v>
       </c>
       <c r="N24" s="3">
         <v>200</v>
@@ -2362,22 +2408,22 @@
         <v>200</v>
       </c>
       <c r="S24" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="T24" s="3">
         <v>400</v>
       </c>
       <c r="U24" s="3">
+        <v>400</v>
+      </c>
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>200</v>
-      </c>
-      <c r="X24" s="3">
-        <v>300</v>
       </c>
       <c r="Y24" s="3">
         <v>300</v>
@@ -2392,34 +2438,37 @@
         <v>300</v>
       </c>
       <c r="AC24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD24" s="3">
         <v>1900</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AF24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG24" s="3">
         <v>1100</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI24" s="3">
-        <v>0</v>
+      <c r="AI24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
         <v>1100</v>
       </c>
-      <c r="AK24" s="3" t="s">
+      <c r="AL24" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,16 +2574,19 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1100</v>
-      </c>
-      <c r="E26" s="3">
-        <v>1200</v>
       </c>
       <c r="F26" s="3">
         <v>1200</v>
@@ -2543,105 +2595,108 @@
         <v>1200</v>
       </c>
       <c r="H26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I26" s="3">
         <v>2500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>600</v>
-      </c>
-      <c r="P26" s="3">
-        <v>700</v>
       </c>
       <c r="Q26" s="3">
         <v>700</v>
       </c>
       <c r="R26" s="3">
+        <v>700</v>
+      </c>
+      <c r="S26" s="3">
         <v>800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6000</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>700</v>
       </c>
       <c r="AE26" s="3">
         <v>700</v>
       </c>
       <c r="AF26" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1100</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1200</v>
       </c>
       <c r="F27" s="3">
         <v>1200</v>
@@ -2650,97 +2705,100 @@
         <v>1200</v>
       </c>
       <c r="H27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I27" s="3">
         <v>2500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>600</v>
-      </c>
-      <c r="P27" s="3">
-        <v>700</v>
       </c>
       <c r="Q27" s="3">
         <v>700</v>
       </c>
       <c r="R27" s="3">
+        <v>700</v>
+      </c>
+      <c r="S27" s="3">
         <v>800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6000</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>700</v>
       </c>
       <c r="AE27" s="3">
         <v>700</v>
       </c>
       <c r="AF27" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2936,11 +2997,11 @@
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-500</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>4</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3196,77 +3266,77 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-1300</v>
       </c>
       <c r="P32" s="3">
         <v>-1300</v>
       </c>
       <c r="Q32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-1700</v>
       </c>
       <c r="Y32" s="3">
         <v>-1700</v>
       </c>
       <c r="Z32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-1600</v>
       </c>
       <c r="AB32" s="3">
         <v>-1600</v>
       </c>
       <c r="AC32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-1100</v>
       </c>
       <c r="AJ32" s="3">
         <v>-1100</v>
@@ -3274,16 +3344,19 @@
       <c r="AK32" s="3">
         <v>-1100</v>
       </c>
+      <c r="AL32" s="3">
+        <v>-1100</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1100</v>
-      </c>
-      <c r="E33" s="3">
-        <v>1200</v>
       </c>
       <c r="F33" s="3">
         <v>1200</v>
@@ -3292,97 +3365,100 @@
         <v>1200</v>
       </c>
       <c r="H33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I33" s="3">
         <v>2500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>600</v>
-      </c>
-      <c r="P33" s="3">
-        <v>700</v>
       </c>
       <c r="Q33" s="3">
         <v>700</v>
       </c>
       <c r="R33" s="3">
+        <v>700</v>
+      </c>
+      <c r="S33" s="3">
         <v>800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6000</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>700</v>
       </c>
       <c r="AE33" s="3">
         <v>700</v>
       </c>
       <c r="AF33" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,16 +3564,19 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1100</v>
-      </c>
-      <c r="E35" s="3">
-        <v>1200</v>
       </c>
       <c r="F35" s="3">
         <v>1200</v>
@@ -3506,209 +3585,215 @@
         <v>1200</v>
       </c>
       <c r="H35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I35" s="3">
         <v>2500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>600</v>
-      </c>
-      <c r="P35" s="3">
-        <v>700</v>
       </c>
       <c r="Q35" s="3">
         <v>700</v>
       </c>
       <c r="R35" s="3">
+        <v>700</v>
+      </c>
+      <c r="S35" s="3">
         <v>800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6000</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>700</v>
       </c>
       <c r="AE35" s="3">
         <v>700</v>
       </c>
       <c r="AF35" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,13 +3871,14 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
@@ -3803,11 +3890,11 @@
         <v>0</v>
       </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
       <c r="J41" s="3">
         <v>0</v>
       </c>
@@ -3842,11 +3929,11 @@
         <v>0</v>
       </c>
       <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3">
         <v>100</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
       <c r="W41" s="3">
         <v>0</v>
       </c>
@@ -3892,8 +3979,11 @@
       <c r="AK41" s="3">
         <v>0</v>
       </c>
+      <c r="AL41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3999,115 +4089,121 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>111600</v>
+      </c>
+      <c r="E43" s="3">
         <v>110800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>109700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>108600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>107500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>106800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>105300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>103700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>101900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>99200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>97700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>97200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>96300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>95800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>94800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>94300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>90500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>89500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>88300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>87500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>86200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>85600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>84200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>83500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>82100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>81700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>51800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>50800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>49600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>50400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>48300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>39300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>37800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4213,8 +4309,11 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4242,8 +4341,8 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -4320,38 +4419,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>111800</v>
+      </c>
+      <c r="E46" s="3">
         <v>110800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>109700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>108700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>107500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>106900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>105300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>103700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>101900</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4427,8 +4529,11 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4456,86 +4561,89 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3">
         <v>11800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>14000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>14000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>14000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>14000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>14000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>14000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>13600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>15100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>22900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>23700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4563,8 +4671,8 @@
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -4618,7 +4726,7 @@
         <v>0</v>
       </c>
       <c r="AD48" s="3">
-        <v>22700</v>
+        <v>0</v>
       </c>
       <c r="AE48" s="3">
         <v>22700</v>
@@ -4641,8 +4749,11 @@
       <c r="AK48" s="3">
         <v>22700</v>
       </c>
+      <c r="AL48" s="3">
+        <v>22700</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,8 +5079,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4991,8 +5111,8 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -5069,8 +5189,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>122900</v>
+      </c>
+      <c r="E54" s="3">
         <v>121900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>120800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>119800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>118700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>118100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>116500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>114900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>113100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>112000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>110700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>109500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>108700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>108100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>107400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>106600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>105800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>104500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>103100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>102400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>101100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>100300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>99200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>98200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>97100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>96100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>95300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>89300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>88600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>87900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>88700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>88100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>87100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>86400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,28 +5491,29 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
+      <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
@@ -5468,8 +5599,11 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5575,8 +5709,11 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5604,8 +5741,8 @@
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -5682,28 +5819,31 @@
       <c r="AK59" s="3">
         <v>0</v>
       </c>
+      <c r="AL59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E60" s="3">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G60" s="3">
-        <v>0</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
+      <c r="D60" s="3">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J60" s="3">
         <v>0</v>
@@ -5789,8 +5929,11 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5896,8 +6039,11 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5925,8 +6071,8 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -6003,8 +6149,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,28 +6479,31 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E66" s="3">
-        <v>0</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G66" s="3">
-        <v>0</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I66" s="3">
-        <v>0</v>
+      <c r="D66" s="3">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J66" s="3">
         <v>0</v>
@@ -6431,8 +6589,11 @@
       <c r="AK66" s="3">
         <v>0</v>
       </c>
+      <c r="AL66" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>62700</v>
+      </c>
+      <c r="E72" s="3">
         <v>61700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>60600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>59400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>58200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>57000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>54600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>52900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>51100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>50000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>48800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>47600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>46700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>46100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>45400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>44700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>43900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>42500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>41200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>40400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>39100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>38300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>37200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>36200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>35100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>34100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>33300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>27300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>26600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>25900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>26800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>26200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>25200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>24400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>122900</v>
+      </c>
+      <c r="E76" s="3">
         <v>121900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>120800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>119800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>118700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>118100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>116500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>114900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>113000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>112000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>110700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>109500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>108700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>108100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>107300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>106600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>105800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>104500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>103100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>102300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>101100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>100200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>99200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>98200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>97100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>96100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>95300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>89300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>88600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>87900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>88700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>88100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>87100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>86400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,128 +7729,134 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1100</v>
-      </c>
-      <c r="E81" s="3">
-        <v>1200</v>
       </c>
       <c r="F81" s="3">
         <v>1200</v>
@@ -7670,97 +7865,100 @@
         <v>1200</v>
       </c>
       <c r="H81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I81" s="3">
         <v>2500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>600</v>
-      </c>
-      <c r="P81" s="3">
-        <v>700</v>
       </c>
       <c r="Q81" s="3">
         <v>700</v>
       </c>
       <c r="R81" s="3">
+        <v>700</v>
+      </c>
+      <c r="S81" s="3">
         <v>800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6000</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>700</v>
       </c>
       <c r="AE81" s="3">
         <v>700</v>
       </c>
       <c r="AF81" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7827,8 +8026,8 @@
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -7905,8 +8104,11 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,29 +8654,32 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>200</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1000</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
         <v>0</v>
       </c>
@@ -8482,73 +8699,76 @@
         <v>0</v>
       </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-9800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>9200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,8 +8806,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8615,8 +8836,8 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8693,8 +8914,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,19 +9134,22 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
+      <c r="F94" s="3">
+        <v>0</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>4</v>
@@ -8936,8 +9166,8 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -8958,64 +9188,67 @@
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>3000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>9800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>1000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,8 +9316,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,29 +9724,32 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-900</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
@@ -9516,8 +9762,8 @@
       <c r="M100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -9588,8 +9834,11 @@
       <c r="AK100" s="3">
         <v>0</v>
       </c>
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,8 +9866,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9695,13 +9944,16 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
@@ -9713,11 +9965,11 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
@@ -9800,6 +10052,9 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="92">
   <si>
     <t>IOR</t>
   </si>
@@ -656,162 +656,166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -842,8 +846,8 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -920,8 +924,11 @@
       <c r="AL8" s="3">
         <v>0</v>
       </c>
+      <c r="AM8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1030,8 +1037,11 @@
       <c r="AL9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1140,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1432,8 +1452,8 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1510,8 +1530,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,8 +1683,9 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1678,49 +1705,49 @@
         <v>100</v>
       </c>
       <c r="I17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
         <v>400</v>
-      </c>
-      <c r="K17" s="3">
-        <v>500</v>
       </c>
       <c r="L17" s="3">
         <v>500</v>
       </c>
       <c r="M17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N17" s="3">
         <v>400</v>
       </c>
       <c r="O17" s="3">
+        <v>400</v>
+      </c>
+      <c r="P17" s="3">
         <v>300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>300</v>
-      </c>
-      <c r="W17" s="3">
-        <v>400</v>
       </c>
       <c r="X17" s="3">
         <v>400</v>
@@ -1738,16 +1765,16 @@
         <v>400</v>
       </c>
       <c r="AC17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD17" s="3">
         <v>500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>400</v>
-      </c>
-      <c r="AF17" s="3">
-        <v>300</v>
       </c>
       <c r="AG17" s="3">
         <v>300</v>
@@ -1756,19 +1783,22 @@
         <v>300</v>
       </c>
       <c r="AI17" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AJ17" s="3">
         <v>400</v>
       </c>
       <c r="AK17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AL17" s="3">
         <v>300</v>
       </c>
+      <c r="AM17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1788,49 +1818,49 @@
         <v>-100</v>
       </c>
       <c r="I18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>-400</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-500</v>
       </c>
       <c r="L18" s="3">
         <v>-500</v>
       </c>
       <c r="M18" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="N18" s="3">
         <v>-400</v>
       </c>
       <c r="O18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P18" s="3">
         <v>-300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-300</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-400</v>
       </c>
       <c r="X18" s="3">
         <v>-400</v>
@@ -1848,16 +1878,16 @@
         <v>-400</v>
       </c>
       <c r="AC18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-400</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>-300</v>
       </c>
       <c r="AG18" s="3">
         <v>-300</v>
@@ -1866,19 +1896,22 @@
         <v>-300</v>
       </c>
       <c r="AI18" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="AJ18" s="3">
         <v>-400</v>
       </c>
       <c r="AK18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AL18" s="3">
         <v>-300</v>
       </c>
+      <c r="AM18" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1949,77 +1983,77 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1400</v>
-      </c>
-      <c r="P20" s="3">
-        <v>1300</v>
       </c>
       <c r="Q20" s="3">
         <v>1300</v>
       </c>
       <c r="R20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S20" s="3">
         <v>1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1500</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>1700</v>
       </c>
       <c r="Z20" s="3">
         <v>1700</v>
       </c>
       <c r="AA20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AB20" s="3">
         <v>1800</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>1600</v>
       </c>
       <c r="AC20" s="3">
         <v>1600</v>
       </c>
       <c r="AD20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AE20" s="3">
         <v>8500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1400</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>1100</v>
       </c>
       <c r="AK20" s="3">
         <v>1100</v>
@@ -2027,8 +2061,11 @@
       <c r="AL20" s="3">
         <v>1100</v>
       </c>
+      <c r="AM20" s="3">
+        <v>1100</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2048,19 +2085,19 @@
         <v>-100</v>
       </c>
       <c r="I21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-400</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-500</v>
       </c>
       <c r="L21" s="3">
         <v>-500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
+      <c r="M21" s="3">
+        <v>-500</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
@@ -2137,8 +2174,11 @@
       <c r="AL21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2169,8 +2209,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2232,8 +2272,8 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>4</v>
+      <c r="AH22" s="3">
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="s">
         <v>4</v>
@@ -2241,14 +2281,17 @@
       <c r="AJ22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK22" s="3">
-        <v>0</v>
+      <c r="AK22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2256,10 +2299,10 @@
         <v>1300</v>
       </c>
       <c r="E23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F23" s="3">
         <v>1400</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1500</v>
       </c>
       <c r="G23" s="3">
         <v>1500</v>
@@ -2268,97 +2311,100 @@
         <v>1500</v>
       </c>
       <c r="I23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J23" s="3">
         <v>2900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>800</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>900</v>
       </c>
       <c r="R23" s="3">
         <v>900</v>
       </c>
       <c r="S23" s="3">
+        <v>900</v>
+      </c>
+      <c r="T23" s="3">
         <v>1000</v>
-      </c>
-      <c r="T23" s="3">
-        <v>1700</v>
       </c>
       <c r="U23" s="3">
         <v>1700</v>
       </c>
       <c r="V23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W23" s="3">
         <v>1000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>1300</v>
       </c>
       <c r="Z23" s="3">
         <v>1300</v>
       </c>
       <c r="AA23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AB23" s="3">
         <v>1400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>7900</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>700</v>
       </c>
       <c r="AF23" s="3">
         <v>700</v>
       </c>
       <c r="AG23" s="3">
+        <v>700</v>
+      </c>
+      <c r="AH23" s="3">
         <v>800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>700</v>
-      </c>
-      <c r="AK23" s="3">
-        <v>800</v>
       </c>
       <c r="AL23" s="3">
         <v>800</v>
       </c>
+      <c r="AM23" s="3">
+        <v>800</v>
+      </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2378,22 +2424,22 @@
         <v>300</v>
       </c>
       <c r="I24" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J24" s="3">
         <v>400</v>
       </c>
       <c r="K24" s="3">
+        <v>400</v>
+      </c>
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
-      </c>
-      <c r="N24" s="3">
-        <v>200</v>
       </c>
       <c r="O24" s="3">
         <v>200</v>
@@ -2411,22 +2457,22 @@
         <v>200</v>
       </c>
       <c r="T24" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="U24" s="3">
         <v>400</v>
       </c>
       <c r="V24" s="3">
+        <v>400</v>
+      </c>
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>200</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>300</v>
       </c>
       <c r="Z24" s="3">
         <v>300</v>
@@ -2441,34 +2487,37 @@
         <v>300</v>
       </c>
       <c r="AD24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE24" s="3">
         <v>1900</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AG24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH24" s="3">
         <v>1100</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ24" s="3">
-        <v>0</v>
+      <c r="AJ24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="3">
         <v>1100</v>
       </c>
-      <c r="AL24" s="3" t="s">
+      <c r="AM24" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,8 +2626,11 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2586,10 +2638,10 @@
         <v>1000</v>
       </c>
       <c r="E26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F26" s="3">
         <v>1100</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1200</v>
       </c>
       <c r="G26" s="3">
         <v>1200</v>
@@ -2598,97 +2650,100 @@
         <v>1200</v>
       </c>
       <c r="I26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J26" s="3">
         <v>2500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>600</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>700</v>
       </c>
       <c r="R26" s="3">
         <v>700</v>
       </c>
       <c r="S26" s="3">
+        <v>700</v>
+      </c>
+      <c r="T26" s="3">
         <v>800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>6000</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>700</v>
       </c>
       <c r="AF26" s="3">
         <v>700</v>
       </c>
       <c r="AG26" s="3">
+        <v>700</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2696,10 +2751,10 @@
         <v>1000</v>
       </c>
       <c r="E27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F27" s="3">
         <v>1100</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1200</v>
       </c>
       <c r="G27" s="3">
         <v>1200</v>
@@ -2708,97 +2763,100 @@
         <v>1200</v>
       </c>
       <c r="I27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J27" s="3">
         <v>2500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>600</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>700</v>
       </c>
       <c r="R27" s="3">
         <v>700</v>
       </c>
       <c r="S27" s="3">
+        <v>700</v>
+      </c>
+      <c r="T27" s="3">
         <v>800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>6000</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>700</v>
       </c>
       <c r="AF27" s="3">
         <v>700</v>
       </c>
       <c r="AG27" s="3">
+        <v>700</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3000,11 +3061,11 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-500</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>4</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3269,77 +3339,77 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>-2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-1300</v>
       </c>
       <c r="Q32" s="3">
         <v>-1300</v>
       </c>
       <c r="R32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="S32" s="3">
         <v>-1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-1700</v>
       </c>
       <c r="Z32" s="3">
         <v>-1700</v>
       </c>
       <c r="AA32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-1600</v>
       </c>
       <c r="AC32" s="3">
         <v>-1600</v>
       </c>
       <c r="AD32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>-1100</v>
       </c>
       <c r="AK32" s="3">
         <v>-1100</v>
@@ -3347,8 +3417,11 @@
       <c r="AL32" s="3">
         <v>-1100</v>
       </c>
+      <c r="AM32" s="3">
+        <v>-1100</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3356,10 +3429,10 @@
         <v>1000</v>
       </c>
       <c r="E33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F33" s="3">
         <v>1100</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1200</v>
       </c>
       <c r="G33" s="3">
         <v>1200</v>
@@ -3368,97 +3441,100 @@
         <v>1200</v>
       </c>
       <c r="I33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J33" s="3">
         <v>2500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>600</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>700</v>
       </c>
       <c r="R33" s="3">
         <v>700</v>
       </c>
       <c r="S33" s="3">
+        <v>700</v>
+      </c>
+      <c r="T33" s="3">
         <v>800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>6000</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>700</v>
       </c>
       <c r="AF33" s="3">
         <v>700</v>
       </c>
       <c r="AG33" s="3">
+        <v>700</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,8 +3643,11 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3576,10 +3655,10 @@
         <v>1000</v>
       </c>
       <c r="E35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F35" s="3">
         <v>1100</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1200</v>
       </c>
       <c r="G35" s="3">
         <v>1200</v>
@@ -3588,212 +3667,218 @@
         <v>1200</v>
       </c>
       <c r="I35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J35" s="3">
         <v>2500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>600</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>700</v>
       </c>
       <c r="R35" s="3">
         <v>700</v>
       </c>
       <c r="S35" s="3">
+        <v>700</v>
+      </c>
+      <c r="T35" s="3">
         <v>800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>6000</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>700</v>
       </c>
       <c r="AF35" s="3">
         <v>700</v>
       </c>
       <c r="AG35" s="3">
+        <v>700</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,17 +3958,18 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
         <v>200</v>
       </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
       <c r="F41" s="3">
         <v>0</v>
       </c>
@@ -3893,11 +3980,11 @@
         <v>0</v>
       </c>
       <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
       <c r="K41" s="3">
         <v>0</v>
       </c>
@@ -3932,11 +4019,11 @@
         <v>0</v>
       </c>
       <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
         <v>100</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
       <c r="X41" s="3">
         <v>0</v>
       </c>
@@ -3982,8 +4069,11 @@
       <c r="AL41" s="3">
         <v>0</v>
       </c>
+      <c r="AM41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4092,118 +4182,124 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>112700</v>
+      </c>
+      <c r="E43" s="3">
         <v>111600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>110800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>109700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>108600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>107500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>106800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>105300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>103700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>101900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>100100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>99200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>97700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>97200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>96300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>95800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>94800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>94300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>90500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>89500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>88300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>87500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>86200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>85600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>84200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>83500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>82100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>81700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>51800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>50800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>49600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>50400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>48300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>39300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>37800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,8 +4408,11 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4344,8 +4443,8 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -4422,41 +4521,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>112800</v>
+      </c>
+      <c r="E46" s="3">
         <v>111800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>110800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>109700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>108700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>107500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>106900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>105300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>103700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>101900</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4532,8 +4634,11 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4564,86 +4669,89 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>11800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>11500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>14000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>14000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>14000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>14000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>14000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>13600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>14000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>13600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>15100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>22900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>23700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4674,8 +4782,8 @@
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -4729,7 +4837,7 @@
         <v>0</v>
       </c>
       <c r="AE48" s="3">
-        <v>22700</v>
+        <v>0</v>
       </c>
       <c r="AF48" s="3">
         <v>22700</v>
@@ -4752,8 +4860,11 @@
       <c r="AL48" s="3">
         <v>22700</v>
       </c>
+      <c r="AM48" s="3">
+        <v>22700</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,8 +5199,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5114,8 +5234,8 @@
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -5192,8 +5312,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>123900</v>
+      </c>
+      <c r="E54" s="3">
         <v>122900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>121900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>120800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>119800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>118700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>118100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>116500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>114900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>113100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>112000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>110700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>109500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>108700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>108100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>107400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>106600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>105800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>104500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>103100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>102400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>101100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>100300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>99200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>98200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>97100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>96100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>95300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>89300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>88600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>87900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>88700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>88100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>87100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>86400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,31 +5622,32 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
         <v>0</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5602,8 +5733,11 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5712,8 +5846,11 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5744,8 +5881,8 @@
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -5822,31 +5959,34 @@
       <c r="AL59" s="3">
         <v>0</v>
       </c>
+      <c r="AM59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
         <v>0</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F60" s="3">
-        <v>0</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H60" s="3">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J60" s="3">
-        <v>0</v>
+      <c r="E60" s="3">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" s="3">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5932,8 +6072,11 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6042,8 +6185,11 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6074,8 +6220,8 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,31 +6637,34 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
         <v>0</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F66" s="3">
-        <v>0</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H66" s="3">
-        <v>0</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J66" s="3">
-        <v>0</v>
+      <c r="E66" s="3">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G66" s="3">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K66" s="3">
         <v>0</v>
@@ -6592,8 +6750,11 @@
       <c r="AL66" s="3">
         <v>0</v>
       </c>
+      <c r="AM66" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E72" s="3">
         <v>62700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>61700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>60600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>59400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>58200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>57000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>54600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>52900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>51100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>50000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>48800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>47600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>46700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>46100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>45400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>44700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>43900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>42500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>41200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>40400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>39100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>38300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>37200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>36200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>35100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>34100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>33300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>27300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>26600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>25900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>26800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>26200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>25200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>24400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>123900</v>
+      </c>
+      <c r="E76" s="3">
         <v>122900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>121900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>120800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>119800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>118700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>118100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>116500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>114900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>113000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>112000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>110700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>109500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>108700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>108100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>107300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>106600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>105800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>104500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>103100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>102300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>101100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>100200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>99200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>98200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>97100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>96100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>95300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>89300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>88600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>87900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>88700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>88100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>87100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>86400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,123 +7921,129 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7856,10 +8051,10 @@
         <v>1000</v>
       </c>
       <c r="E81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F81" s="3">
         <v>1100</v>
-      </c>
-      <c r="F81" s="3">
-        <v>1200</v>
       </c>
       <c r="G81" s="3">
         <v>1200</v>
@@ -7868,97 +8063,100 @@
         <v>1200</v>
       </c>
       <c r="I81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J81" s="3">
         <v>2500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>600</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>700</v>
       </c>
       <c r="R81" s="3">
         <v>700</v>
       </c>
       <c r="S81" s="3">
+        <v>700</v>
+      </c>
+      <c r="T81" s="3">
         <v>800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>6000</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>700</v>
       </c>
       <c r="AF81" s="3">
         <v>700</v>
       </c>
       <c r="AG81" s="3">
+        <v>700</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8029,8 +8228,8 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,32 +8871,35 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>100</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>200</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1000</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
         <v>0</v>
       </c>
@@ -8702,73 +8919,76 @@
         <v>0</v>
       </c>
       <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>-8300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-9800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>9200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,8 +9027,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8839,8 +9060,8 @@
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8917,8 +9138,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,22 +9364,25 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>4</v>
@@ -9169,8 +9399,8 @@
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -9191,64 +9421,67 @@
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>3000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>9800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>1000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,32 +9970,35 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-900</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
@@ -9765,8 +10011,8 @@
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
@@ -9837,8 +10083,11 @@
       <c r="AL100" s="3">
         <v>0</v>
       </c>
+      <c r="AM100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,17 +10196,20 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
@@ -9968,11 +10220,11 @@
         <v>0</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
@@ -10055,6 +10307,9 @@
         <v>0</v>
       </c>
       <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="92">
   <si>
     <t>IOR</t>
   </si>
@@ -656,170 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -856,8 +859,8 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -934,8 +937,11 @@
       <c r="AN8" s="3">
         <v>0</v>
       </c>
+      <c r="AO8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1050,8 +1056,11 @@
       <c r="AN9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1175,11 @@
       <c r="AN10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1324,8 +1337,11 @@
       <c r="AN12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,8 +1456,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1478,8 +1497,8 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1556,8 +1575,11 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1672,8 +1694,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,8 +1736,9 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1738,49 +1764,49 @@
         <v>100</v>
       </c>
       <c r="K17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
         <v>400</v>
-      </c>
-      <c r="M17" s="3">
-        <v>500</v>
       </c>
       <c r="N17" s="3">
         <v>500</v>
       </c>
       <c r="O17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="P17" s="3">
         <v>400</v>
       </c>
       <c r="Q17" s="3">
+        <v>400</v>
+      </c>
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>300</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>400</v>
       </c>
       <c r="Z17" s="3">
         <v>400</v>
@@ -1798,16 +1824,16 @@
         <v>400</v>
       </c>
       <c r="AE17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF17" s="3">
         <v>500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>400</v>
-      </c>
-      <c r="AH17" s="3">
-        <v>300</v>
       </c>
       <c r="AI17" s="3">
         <v>300</v>
@@ -1816,19 +1842,22 @@
         <v>300</v>
       </c>
       <c r="AK17" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AL17" s="3">
         <v>400</v>
       </c>
       <c r="AM17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AN17" s="3">
         <v>300</v>
       </c>
+      <c r="AO17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1854,49 +1883,49 @@
         <v>-100</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
         <v>-400</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-500</v>
       </c>
       <c r="N18" s="3">
         <v>-500</v>
       </c>
       <c r="O18" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="P18" s="3">
         <v>-400</v>
       </c>
       <c r="Q18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R18" s="3">
         <v>-300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-400</v>
       </c>
       <c r="Z18" s="3">
         <v>-400</v>
@@ -1914,16 +1943,16 @@
         <v>-400</v>
       </c>
       <c r="AE18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-400</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>-300</v>
       </c>
       <c r="AI18" s="3">
         <v>-300</v>
@@ -1932,19 +1961,22 @@
         <v>-300</v>
       </c>
       <c r="AK18" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="AL18" s="3">
         <v>-400</v>
       </c>
       <c r="AM18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AN18" s="3">
         <v>-300</v>
       </c>
+      <c r="AO18" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,8 +2017,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2023,77 +2056,77 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>2100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1400</v>
-      </c>
-      <c r="R20" s="3">
-        <v>1300</v>
       </c>
       <c r="S20" s="3">
         <v>1300</v>
       </c>
       <c r="T20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U20" s="3">
         <v>1200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1500</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>1700</v>
       </c>
       <c r="AB20" s="3">
         <v>1700</v>
       </c>
       <c r="AC20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AD20" s="3">
         <v>1800</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>1600</v>
       </c>
       <c r="AE20" s="3">
         <v>1600</v>
       </c>
       <c r="AF20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AG20" s="3">
         <v>8500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1400</v>
-      </c>
-      <c r="AL20" s="3">
-        <v>1100</v>
       </c>
       <c r="AM20" s="3">
         <v>1100</v>
@@ -2101,8 +2134,11 @@
       <c r="AN20" s="3">
         <v>1100</v>
       </c>
+      <c r="AO20" s="3">
+        <v>1100</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2128,19 +2164,19 @@
         <v>-100</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
         <v>-400</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-500</v>
       </c>
       <c r="N21" s="3">
         <v>-500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
+      <c r="O21" s="3">
+        <v>-500</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
@@ -2217,8 +2253,11 @@
       <c r="AN21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2255,8 +2294,8 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2318,8 +2357,8 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
-      <c r="AJ22" s="3" t="s">
-        <v>4</v>
+      <c r="AJ22" s="3">
+        <v>0</v>
       </c>
       <c r="AK22" s="3" t="s">
         <v>4</v>
@@ -2327,19 +2366,22 @@
       <c r="AL22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AM22" s="3">
-        <v>0</v>
+      <c r="AM22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="E23" s="3">
         <v>1300</v>
@@ -2348,10 +2390,10 @@
         <v>1300</v>
       </c>
       <c r="G23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H23" s="3">
         <v>1400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1500</v>
       </c>
       <c r="I23" s="3">
         <v>1500</v>
@@ -2360,97 +2402,100 @@
         <v>1500</v>
       </c>
       <c r="K23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L23" s="3">
         <v>2900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>800</v>
-      </c>
-      <c r="S23" s="3">
-        <v>900</v>
       </c>
       <c r="T23" s="3">
         <v>900</v>
       </c>
       <c r="U23" s="3">
+        <v>900</v>
+      </c>
+      <c r="V23" s="3">
         <v>1000</v>
-      </c>
-      <c r="V23" s="3">
-        <v>1700</v>
       </c>
       <c r="W23" s="3">
         <v>1700</v>
       </c>
       <c r="X23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y23" s="3">
         <v>1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1100</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>1300</v>
       </c>
       <c r="AB23" s="3">
         <v>1300</v>
       </c>
       <c r="AC23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AD23" s="3">
         <v>1400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>7900</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>700</v>
       </c>
       <c r="AH23" s="3">
         <v>700</v>
       </c>
       <c r="AI23" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>700</v>
-      </c>
-      <c r="AM23" s="3">
-        <v>800</v>
       </c>
       <c r="AN23" s="3">
         <v>800</v>
       </c>
+      <c r="AO23" s="3">
+        <v>800</v>
+      </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2476,22 +2521,22 @@
         <v>300</v>
       </c>
       <c r="K24" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L24" s="3">
         <v>400</v>
       </c>
       <c r="M24" s="3">
+        <v>400</v>
+      </c>
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
-      </c>
-      <c r="P24" s="3">
-        <v>200</v>
       </c>
       <c r="Q24" s="3">
         <v>200</v>
@@ -2509,22 +2554,22 @@
         <v>200</v>
       </c>
       <c r="V24" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="W24" s="3">
         <v>400</v>
       </c>
       <c r="X24" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>200</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>300</v>
       </c>
       <c r="AB24" s="3">
         <v>300</v>
@@ -2539,34 +2584,37 @@
         <v>300</v>
       </c>
       <c r="AF24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG24" s="3">
         <v>1900</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AI24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AL24" s="3">
-        <v>0</v>
+      <c r="AL24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AM24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="3">
         <v>1100</v>
       </c>
-      <c r="AN24" s="3" t="s">
+      <c r="AO24" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,8 +2729,11 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2696,10 +2747,10 @@
         <v>1000</v>
       </c>
       <c r="G26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H26" s="3">
         <v>1100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1200</v>
       </c>
       <c r="I26" s="3">
         <v>1200</v>
@@ -2708,97 +2759,100 @@
         <v>1200</v>
       </c>
       <c r="K26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L26" s="3">
         <v>2500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>600</v>
-      </c>
-      <c r="S26" s="3">
-        <v>700</v>
       </c>
       <c r="T26" s="3">
         <v>700</v>
       </c>
       <c r="U26" s="3">
+        <v>700</v>
+      </c>
+      <c r="V26" s="3">
         <v>800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6000</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>700</v>
       </c>
       <c r="AH26" s="3">
         <v>700</v>
       </c>
       <c r="AI26" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2812,10 +2866,10 @@
         <v>1000</v>
       </c>
       <c r="G27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H27" s="3">
         <v>1100</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1200</v>
       </c>
       <c r="I27" s="3">
         <v>1200</v>
@@ -2824,97 +2878,100 @@
         <v>1200</v>
       </c>
       <c r="K27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L27" s="3">
         <v>2500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>600</v>
-      </c>
-      <c r="S27" s="3">
-        <v>700</v>
       </c>
       <c r="T27" s="3">
         <v>700</v>
       </c>
       <c r="U27" s="3">
+        <v>700</v>
+      </c>
+      <c r="V27" s="3">
         <v>800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6000</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>700</v>
       </c>
       <c r="AH27" s="3">
         <v>700</v>
       </c>
       <c r="AI27" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3128,11 +3188,11 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>4</v>
       </c>
@@ -3145,8 +3205,11 @@
       <c r="AN29" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,8 +3443,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3415,77 +3484,77 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>-2100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-1300</v>
       </c>
       <c r="S32" s="3">
         <v>-1300</v>
       </c>
       <c r="T32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="U32" s="3">
         <v>-1200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-1700</v>
       </c>
       <c r="AB32" s="3">
         <v>-1700</v>
       </c>
       <c r="AC32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-1600</v>
       </c>
       <c r="AE32" s="3">
         <v>-1600</v>
       </c>
       <c r="AF32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AL32" s="3">
-        <v>-1100</v>
       </c>
       <c r="AM32" s="3">
         <v>-1100</v>
@@ -3493,8 +3562,11 @@
       <c r="AN32" s="3">
         <v>-1100</v>
       </c>
+      <c r="AO32" s="3">
+        <v>-1100</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3508,10 +3580,10 @@
         <v>1000</v>
       </c>
       <c r="G33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H33" s="3">
         <v>1100</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1200</v>
       </c>
       <c r="I33" s="3">
         <v>1200</v>
@@ -3520,97 +3592,100 @@
         <v>1200</v>
       </c>
       <c r="K33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L33" s="3">
         <v>2500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>600</v>
-      </c>
-      <c r="S33" s="3">
-        <v>700</v>
       </c>
       <c r="T33" s="3">
         <v>700</v>
       </c>
       <c r="U33" s="3">
+        <v>700</v>
+      </c>
+      <c r="V33" s="3">
         <v>800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6000</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>700</v>
       </c>
       <c r="AH33" s="3">
         <v>700</v>
       </c>
       <c r="AI33" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,8 +3800,11 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3740,10 +3818,10 @@
         <v>1000</v>
       </c>
       <c r="G35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H35" s="3">
         <v>1100</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1200</v>
       </c>
       <c r="I35" s="3">
         <v>1200</v>
@@ -3752,218 +3830,224 @@
         <v>1200</v>
       </c>
       <c r="K35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L35" s="3">
         <v>2500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>600</v>
-      </c>
-      <c r="S35" s="3">
-        <v>700</v>
       </c>
       <c r="T35" s="3">
         <v>700</v>
       </c>
       <c r="U35" s="3">
+        <v>700</v>
+      </c>
+      <c r="V35" s="3">
         <v>800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6000</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>700</v>
       </c>
       <c r="AH35" s="3">
         <v>700</v>
       </c>
       <c r="AI35" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,8 +4131,9 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -4055,14 +4141,14 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
         <v>0</v>
       </c>
@@ -4073,11 +4159,11 @@
         <v>0</v>
       </c>
       <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
         <v>100</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
       <c r="M41" s="3">
         <v>0</v>
       </c>
@@ -4112,11 +4198,11 @@
         <v>0</v>
       </c>
       <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
         <v>100</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
       <c r="Z41" s="3">
         <v>0</v>
       </c>
@@ -4162,8 +4248,11 @@
       <c r="AN41" s="3">
         <v>0</v>
       </c>
+      <c r="AO41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4278,124 +4367,130 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>114800</v>
+      </c>
+      <c r="E43" s="3">
         <v>113900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>112700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>111600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>110800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>109700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>108600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>107500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>106800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>105300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>103700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>101900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>100100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>99200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>97700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>97200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>96300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>95800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>94800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>94300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>90500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>89500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>88300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>87500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>86200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>85600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>84200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>83500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>82100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>81700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>51800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>50800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>49600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>50400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>48300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>39300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>37800</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4432,8 +4527,8 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4510,8 +4605,11 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4548,8 +4646,8 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -4626,47 +4724,50 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>114800</v>
+      </c>
+      <c r="E46" s="3">
         <v>113900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>112800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>111800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>110800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>109700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>108700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>107500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>106900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>105300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>103700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>101900</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4742,8 +4843,11 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4780,86 +4884,89 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3">
         <v>11800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>11500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>11800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>11500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>14000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>14000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>14000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>14000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>13600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>14000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>13600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>14000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>13600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>15100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>22900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>23700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4896,8 +5003,8 @@
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -4951,7 +5058,7 @@
         <v>0</v>
       </c>
       <c r="AG48" s="3">
-        <v>22700</v>
+        <v>0</v>
       </c>
       <c r="AH48" s="3">
         <v>22700</v>
@@ -4974,8 +5081,11 @@
       <c r="AN48" s="3">
         <v>22700</v>
       </c>
+      <c r="AO48" s="3">
+        <v>22700</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5090,8 +5200,11 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,8 +5438,11 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5360,8 +5479,8 @@
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -5438,8 +5557,11 @@
       <c r="AN52" s="3">
         <v>0</v>
       </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E54" s="3">
         <v>124900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>123900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>122900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>121900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>120800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>119800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>118700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>118100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>116500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>114900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>113100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>112000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>110700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>109500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>108700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>108100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>107400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>106600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>105800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>104500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>103100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>102400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>101100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>100300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>99200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>98200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>97100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>96100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>95300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>89300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>88600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>87900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>88700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>88100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>87100</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>86400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,13 +5883,14 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
@@ -5768,23 +5898,23 @@
       <c r="F57" s="3">
         <v>0</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -5870,8 +6000,11 @@
       <c r="AN57" s="3">
         <v>0</v>
       </c>
+      <c r="AO57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5986,8 +6119,11 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6024,8 +6160,8 @@
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -6102,13 +6238,16 @@
       <c r="AN59" s="3">
         <v>0</v>
       </c>
+      <c r="AO59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>0</v>
+      <c r="D60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E60" s="3">
         <v>0</v>
@@ -6116,23 +6255,23 @@
       <c r="F60" s="3">
         <v>0</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H60" s="3">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J60" s="3">
-        <v>0</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L60" s="3">
-        <v>0</v>
+      <c r="G60" s="3">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
+        <v>0</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
@@ -6218,8 +6357,11 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6334,8 +6476,11 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6372,8 +6517,8 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -6450,8 +6595,11 @@
       <c r="AN62" s="3">
         <v>0</v>
       </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,13 +6952,16 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>0</v>
+      <c r="D66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E66" s="3">
         <v>0</v>
@@ -6812,23 +6969,23 @@
       <c r="F66" s="3">
         <v>0</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H66" s="3">
-        <v>0</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J66" s="3">
-        <v>0</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L66" s="3">
-        <v>0</v>
+      <c r="G66" s="3">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
+        <v>0</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M66" s="3">
         <v>0</v>
@@ -6914,8 +7071,11 @@
       <c r="AN66" s="3">
         <v>0</v>
       </c>
+      <c r="AO66" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>65700</v>
+      </c>
+      <c r="E72" s="3">
         <v>64700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>63700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>62700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>61700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>60600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>59400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>58200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>57000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>54600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>52900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>51100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>50000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>48800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>47600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>46700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>46100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>45400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>44700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>43900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>42500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>41200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>40400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>39100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>38300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>37200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>36200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>35100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>34100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>33300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>27300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>26600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>25900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>26800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>26200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>25200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>24400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E76" s="3">
         <v>124900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>123900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>122900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>121900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>120800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>119800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>118700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>118100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>116500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>114900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>113000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>112000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>110700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>109500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>108700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>108100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>107300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>106600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>105800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>104500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>103100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>102300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>101100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>100200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>99200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>98200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>97100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>96100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>95300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>89300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>88600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>87900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>88700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>88100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>87100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>86400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,129 +8304,135 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8252,10 +8446,10 @@
         <v>1000</v>
       </c>
       <c r="G81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H81" s="3">
         <v>1100</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1200</v>
       </c>
       <c r="I81" s="3">
         <v>1200</v>
@@ -8264,97 +8458,100 @@
         <v>1200</v>
       </c>
       <c r="K81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L81" s="3">
         <v>2500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>600</v>
-      </c>
-      <c r="S81" s="3">
-        <v>700</v>
       </c>
       <c r="T81" s="3">
         <v>700</v>
       </c>
       <c r="U81" s="3">
+        <v>700</v>
+      </c>
+      <c r="V81" s="3">
         <v>800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6000</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>700</v>
       </c>
       <c r="AH81" s="3">
         <v>700</v>
       </c>
       <c r="AI81" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,8 +8592,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8433,8 +8631,8 @@
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -8511,8 +8709,11 @@
       <c r="AN83" s="3">
         <v>0</v>
       </c>
+      <c r="AO83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,38 +9304,41 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>-200</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>100</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>200</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1000</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
@@ -9142,73 +9358,76 @@
         <v>0</v>
       </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-8300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-9800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>9200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,8 +9468,9 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9287,8 +9507,8 @@
       <c r="N91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -9365,8 +9585,11 @@
       <c r="AN91" s="3">
         <v>0</v>
       </c>
+      <c r="AO91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,28 +9823,31 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>4</v>
@@ -9635,8 +9864,8 @@
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -9657,64 +9886,67 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>3000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>1000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +9987,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9793,8 +10026,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9871,8 +10104,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,8 +10461,11 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10233,24 +10478,24 @@
       <c r="F100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>4</v>
       </c>
@@ -10263,8 +10508,8 @@
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -10335,8 +10580,11 @@
       <c r="AN100" s="3">
         <v>0</v>
       </c>
+      <c r="AO100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10373,8 +10621,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10451,23 +10699,26 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
@@ -10478,11 +10729,11 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
@@ -10565,6 +10816,9 @@
         <v>0</v>
       </c>
       <c r="AN102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="92">
   <si>
     <t>IOR</t>
   </si>
@@ -656,173 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -862,8 +866,8 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -940,8 +944,11 @@
       <c r="AO8" s="3">
         <v>0</v>
       </c>
+      <c r="AP8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1059,8 +1066,11 @@
       <c r="AO9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1178,8 +1188,11 @@
       <c r="AO10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,8 +1476,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1500,8 +1520,8 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1578,8 +1598,11 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1697,8 +1720,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,8 +1763,9 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1767,49 +1794,49 @@
         <v>100</v>
       </c>
       <c r="L17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
         <v>400</v>
-      </c>
-      <c r="N17" s="3">
-        <v>500</v>
       </c>
       <c r="O17" s="3">
         <v>500</v>
       </c>
       <c r="P17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Q17" s="3">
         <v>400</v>
       </c>
       <c r="R17" s="3">
+        <v>400</v>
+      </c>
+      <c r="S17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>300</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>400</v>
       </c>
       <c r="AA17" s="3">
         <v>400</v>
@@ -1827,16 +1854,16 @@
         <v>400</v>
       </c>
       <c r="AF17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG17" s="3">
         <v>500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>400</v>
-      </c>
-      <c r="AI17" s="3">
-        <v>300</v>
       </c>
       <c r="AJ17" s="3">
         <v>300</v>
@@ -1845,19 +1872,22 @@
         <v>300</v>
       </c>
       <c r="AL17" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AM17" s="3">
         <v>400</v>
       </c>
       <c r="AN17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AO17" s="3">
         <v>300</v>
       </c>
+      <c r="AP17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1886,49 +1916,49 @@
         <v>-100</v>
       </c>
       <c r="L18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
         <v>-400</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-500</v>
       </c>
       <c r="O18" s="3">
         <v>-500</v>
       </c>
       <c r="P18" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="Q18" s="3">
         <v>-400</v>
       </c>
       <c r="R18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-400</v>
       </c>
       <c r="AA18" s="3">
         <v>-400</v>
@@ -1946,16 +1976,16 @@
         <v>-400</v>
       </c>
       <c r="AF18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-400</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>-300</v>
       </c>
       <c r="AJ18" s="3">
         <v>-300</v>
@@ -1964,19 +1994,22 @@
         <v>-300</v>
       </c>
       <c r="AL18" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="AM18" s="3">
         <v>-400</v>
       </c>
       <c r="AN18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="AO18" s="3">
         <v>-300</v>
       </c>
+      <c r="AP18" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,8 +2051,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2059,77 +2093,77 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1400</v>
-      </c>
-      <c r="S20" s="3">
-        <v>1300</v>
       </c>
       <c r="T20" s="3">
         <v>1300</v>
       </c>
       <c r="U20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V20" s="3">
         <v>1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1500</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>1700</v>
       </c>
       <c r="AC20" s="3">
         <v>1700</v>
       </c>
       <c r="AD20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AE20" s="3">
         <v>1800</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>1600</v>
       </c>
       <c r="AF20" s="3">
         <v>1600</v>
       </c>
       <c r="AG20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AH20" s="3">
         <v>8500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1400</v>
-      </c>
-      <c r="AM20" s="3">
-        <v>1100</v>
       </c>
       <c r="AN20" s="3">
         <v>1100</v>
@@ -2137,8 +2171,11 @@
       <c r="AO20" s="3">
         <v>1100</v>
       </c>
+      <c r="AP20" s="3">
+        <v>1100</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2167,19 +2204,19 @@
         <v>-100</v>
       </c>
       <c r="L21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-400</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-500</v>
       </c>
       <c r="O21" s="3">
         <v>-500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
+      <c r="P21" s="3">
+        <v>-500</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
@@ -2256,8 +2293,11 @@
       <c r="AO21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2297,8 +2337,8 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2360,8 +2400,8 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
-      <c r="AK22" s="3" t="s">
-        <v>4</v>
+      <c r="AK22" s="3">
+        <v>0</v>
       </c>
       <c r="AL22" s="3" t="s">
         <v>4</v>
@@ -2369,22 +2409,25 @@
       <c r="AM22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AN22" s="3">
-        <v>0</v>
+      <c r="AN22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E23" s="3">
         <v>1200</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1300</v>
       </c>
       <c r="F23" s="3">
         <v>1300</v>
@@ -2393,10 +2436,10 @@
         <v>1300</v>
       </c>
       <c r="H23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I23" s="3">
         <v>1400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>1500</v>
       </c>
       <c r="J23" s="3">
         <v>1500</v>
@@ -2405,97 +2448,100 @@
         <v>1500</v>
       </c>
       <c r="L23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M23" s="3">
         <v>2900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>800</v>
-      </c>
-      <c r="T23" s="3">
-        <v>900</v>
       </c>
       <c r="U23" s="3">
         <v>900</v>
       </c>
       <c r="V23" s="3">
+        <v>900</v>
+      </c>
+      <c r="W23" s="3">
         <v>1000</v>
-      </c>
-      <c r="W23" s="3">
-        <v>1700</v>
       </c>
       <c r="X23" s="3">
         <v>1700</v>
       </c>
       <c r="Y23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Z23" s="3">
         <v>1000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1100</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>1300</v>
       </c>
       <c r="AC23" s="3">
         <v>1300</v>
       </c>
       <c r="AD23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AE23" s="3">
         <v>1400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>7900</v>
-      </c>
-      <c r="AH23" s="3">
-        <v>700</v>
       </c>
       <c r="AI23" s="3">
         <v>700</v>
       </c>
       <c r="AJ23" s="3">
+        <v>700</v>
+      </c>
+      <c r="AK23" s="3">
         <v>800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>700</v>
-      </c>
-      <c r="AN23" s="3">
-        <v>800</v>
       </c>
       <c r="AO23" s="3">
         <v>800</v>
       </c>
+      <c r="AP23" s="3">
+        <v>800</v>
+      </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2524,22 +2570,22 @@
         <v>300</v>
       </c>
       <c r="L24" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M24" s="3">
         <v>400</v>
       </c>
       <c r="N24" s="3">
+        <v>400</v>
+      </c>
+      <c r="O24" s="3">
         <v>500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>200</v>
       </c>
       <c r="R24" s="3">
         <v>200</v>
@@ -2557,22 +2603,22 @@
         <v>200</v>
       </c>
       <c r="W24" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="X24" s="3">
         <v>400</v>
       </c>
       <c r="Y24" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>200</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>300</v>
       </c>
       <c r="AC24" s="3">
         <v>300</v>
@@ -2587,34 +2633,37 @@
         <v>300</v>
       </c>
       <c r="AG24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH24" s="3">
         <v>1900</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AJ24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK24" s="3">
         <v>1100</v>
       </c>
-      <c r="AK24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AM24" s="3">
-        <v>0</v>
+      <c r="AM24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3">
         <v>1100</v>
       </c>
-      <c r="AO24" s="3" t="s">
+      <c r="AP24" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,8 +2781,11 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2750,10 +2802,10 @@
         <v>1000</v>
       </c>
       <c r="H26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I26" s="3">
         <v>1100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1200</v>
       </c>
       <c r="J26" s="3">
         <v>1200</v>
@@ -2762,97 +2814,100 @@
         <v>1200</v>
       </c>
       <c r="L26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M26" s="3">
         <v>2500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>600</v>
-      </c>
-      <c r="T26" s="3">
-        <v>700</v>
       </c>
       <c r="U26" s="3">
         <v>700</v>
       </c>
       <c r="V26" s="3">
+        <v>700</v>
+      </c>
+      <c r="W26" s="3">
         <v>800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6000</v>
-      </c>
-      <c r="AH26" s="3">
-        <v>700</v>
       </c>
       <c r="AI26" s="3">
         <v>700</v>
       </c>
       <c r="AJ26" s="3">
+        <v>700</v>
+      </c>
+      <c r="AK26" s="3">
         <v>-300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2869,10 +2924,10 @@
         <v>1000</v>
       </c>
       <c r="H27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I27" s="3">
         <v>1100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>1200</v>
       </c>
       <c r="J27" s="3">
         <v>1200</v>
@@ -2881,97 +2936,100 @@
         <v>1200</v>
       </c>
       <c r="L27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M27" s="3">
         <v>2500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>600</v>
-      </c>
-      <c r="T27" s="3">
-        <v>700</v>
       </c>
       <c r="U27" s="3">
         <v>700</v>
       </c>
       <c r="V27" s="3">
+        <v>700</v>
+      </c>
+      <c r="W27" s="3">
         <v>800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>6000</v>
-      </c>
-      <c r="AH27" s="3">
-        <v>700</v>
       </c>
       <c r="AI27" s="3">
         <v>700</v>
       </c>
       <c r="AJ27" s="3">
+        <v>700</v>
+      </c>
+      <c r="AK27" s="3">
         <v>-300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3191,11 +3252,11 @@
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-500</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>4</v>
       </c>
@@ -3208,8 +3269,11 @@
       <c r="AO29" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,8 +3513,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3487,77 +3557,77 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-1300</v>
       </c>
       <c r="T32" s="3">
         <v>-1300</v>
       </c>
       <c r="U32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-1700</v>
       </c>
       <c r="AC32" s="3">
         <v>-1700</v>
       </c>
       <c r="AD32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-1600</v>
       </c>
       <c r="AF32" s="3">
         <v>-1600</v>
       </c>
       <c r="AG32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AM32" s="3">
-        <v>-1100</v>
       </c>
       <c r="AN32" s="3">
         <v>-1100</v>
@@ -3565,8 +3635,11 @@
       <c r="AO32" s="3">
         <v>-1100</v>
       </c>
+      <c r="AP32" s="3">
+        <v>-1100</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3583,10 +3656,10 @@
         <v>1000</v>
       </c>
       <c r="H33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I33" s="3">
         <v>1100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1200</v>
       </c>
       <c r="J33" s="3">
         <v>1200</v>
@@ -3595,97 +3668,100 @@
         <v>1200</v>
       </c>
       <c r="L33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M33" s="3">
         <v>2500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>600</v>
-      </c>
-      <c r="T33" s="3">
-        <v>700</v>
       </c>
       <c r="U33" s="3">
         <v>700</v>
       </c>
       <c r="V33" s="3">
+        <v>700</v>
+      </c>
+      <c r="W33" s="3">
         <v>800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6000</v>
-      </c>
-      <c r="AH33" s="3">
-        <v>700</v>
       </c>
       <c r="AI33" s="3">
         <v>700</v>
       </c>
       <c r="AJ33" s="3">
+        <v>700</v>
+      </c>
+      <c r="AK33" s="3">
         <v>-900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,8 +3879,11 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3821,10 +3900,10 @@
         <v>1000</v>
       </c>
       <c r="H35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I35" s="3">
         <v>1100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1200</v>
       </c>
       <c r="J35" s="3">
         <v>1200</v>
@@ -3833,221 +3912,227 @@
         <v>1200</v>
       </c>
       <c r="L35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M35" s="3">
         <v>2500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>600</v>
-      </c>
-      <c r="T35" s="3">
-        <v>700</v>
       </c>
       <c r="U35" s="3">
         <v>700</v>
       </c>
       <c r="V35" s="3">
+        <v>700</v>
+      </c>
+      <c r="W35" s="3">
         <v>800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6000</v>
-      </c>
-      <c r="AH35" s="3">
-        <v>700</v>
       </c>
       <c r="AI35" s="3">
         <v>700</v>
       </c>
       <c r="AJ35" s="3">
+        <v>700</v>
+      </c>
+      <c r="AK35" s="3">
         <v>-900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,8 +4218,9 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -4144,14 +4231,14 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>200</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
       <c r="I41" s="3">
         <v>0</v>
       </c>
@@ -4162,11 +4249,11 @@
         <v>0</v>
       </c>
       <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
       <c r="N41" s="3">
         <v>0</v>
       </c>
@@ -4201,11 +4288,11 @@
         <v>0</v>
       </c>
       <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>100</v>
       </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
       <c r="AA41" s="3">
         <v>0</v>
       </c>
@@ -4251,8 +4338,11 @@
       <c r="AO41" s="3">
         <v>0</v>
       </c>
+      <c r="AP41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4370,127 +4460,133 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E43" s="3">
         <v>114800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>113900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>112700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>111600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>110800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>109700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>108600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>107500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>106800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>105300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>103700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>101900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>100100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>99200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>97700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>97200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>96300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>95800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>94800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>94300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>90500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>89500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>88300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>87500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>86200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>85600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>84200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>83500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>82100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>81700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>51800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>50800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>49600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>50400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>48300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>39300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>37800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4530,8 +4626,8 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4608,8 +4704,11 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4649,8 +4748,8 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q45" s="3">
         <v>0</v>
@@ -4727,50 +4826,53 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E46" s="3">
         <v>114800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>113900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>112800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>111800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>110800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>109700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>108700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>107500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>106900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>105300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>103700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>101900</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4846,8 +4948,11 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4887,86 +4992,89 @@
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="3">
         <v>11800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>11800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>11500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>11800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>11500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>14000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>14000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>14000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>14000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>13600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>14000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>13600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>14000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>13600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>15100</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>22900</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>23700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -5006,8 +5114,8 @@
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -5061,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="AH48" s="3">
-        <v>22700</v>
+        <v>0</v>
       </c>
       <c r="AI48" s="3">
         <v>22700</v>
@@ -5084,8 +5192,11 @@
       <c r="AO48" s="3">
         <v>22700</v>
       </c>
+      <c r="AP48" s="3">
+        <v>22700</v>
+      </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5203,8 +5314,11 @@
       <c r="AO49" s="3">
         <v>0</v>
       </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,8 +5558,11 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5482,8 +5602,8 @@
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -5560,8 +5680,11 @@
       <c r="AO52" s="3">
         <v>0</v>
       </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>126900</v>
+      </c>
+      <c r="E54" s="3">
         <v>125900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>124900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>123900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>122900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>121900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>120800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>119800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>118700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>118100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>116500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>114900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>113100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>112000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>110700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>109500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>108700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>108100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>107400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>106600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>105800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>104500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>103100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>102400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>101100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>100300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>99200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>98200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>97100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>96100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>95300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>89300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>88600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>87900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>88700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>88100</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>87100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>86400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,16 +6014,17 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
+      <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F57" s="3">
         <v>0</v>
@@ -5901,23 +6032,23 @@
       <c r="G57" s="3">
         <v>0</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -6003,8 +6134,11 @@
       <c r="AO57" s="3">
         <v>0</v>
       </c>
+      <c r="AP57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6122,8 +6256,11 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6163,8 +6300,8 @@
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q59" s="3">
         <v>0</v>
@@ -6241,16 +6378,19 @@
       <c r="AO59" s="3">
         <v>0</v>
       </c>
+      <c r="AP59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E60" s="3">
-        <v>0</v>
+      <c r="D60" s="3">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F60" s="3">
         <v>0</v>
@@ -6258,23 +6398,23 @@
       <c r="G60" s="3">
         <v>0</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M60" s="3">
-        <v>0</v>
+      <c r="H60" s="3">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3">
+        <v>0</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N60" s="3">
         <v>0</v>
@@ -6360,8 +6500,11 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6479,8 +6622,11 @@
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6520,8 +6666,8 @@
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -6598,8 +6744,11 @@
       <c r="AO62" s="3">
         <v>0</v>
       </c>
+      <c r="AP62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,16 +7110,19 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E66" s="3">
-        <v>0</v>
+      <c r="D66" s="3">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F66" s="3">
         <v>0</v>
@@ -6972,23 +7130,23 @@
       <c r="G66" s="3">
         <v>0</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I66" s="3">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K66" s="3">
-        <v>0</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M66" s="3">
-        <v>0</v>
+      <c r="H66" s="3">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
+        <v>0</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N66" s="3">
         <v>0</v>
@@ -7074,8 +7232,11 @@
       <c r="AO66" s="3">
         <v>0</v>
       </c>
+      <c r="AP66" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E72" s="3">
         <v>65700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>64700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>63700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>62700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>61700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>60600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>59400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>58200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>57000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>54600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>52900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>51100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>50000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>48800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>47600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>46700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>46100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>45400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>44700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>43900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>42500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>41200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>40400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>39100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>38300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>37200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>36200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>35100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>34100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>33300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>27300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>26600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>25900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>26800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>26200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>25200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>24400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>126900</v>
+      </c>
+      <c r="E76" s="3">
         <v>125900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>124900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>123900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>122900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>121900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>120800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>119800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>118700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>118100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>116500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>114900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>113000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>112000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>110700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>109500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>108700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>108100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>107300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>106600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>105800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>104500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>103100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>102300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>101100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>100200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>99200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>98200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>97100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>96100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>95300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>89300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>88600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>87900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>88700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>88100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>87100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>86400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,132 +8496,138 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8449,10 +8644,10 @@
         <v>1000</v>
       </c>
       <c r="H81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I81" s="3">
         <v>1100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1200</v>
       </c>
       <c r="J81" s="3">
         <v>1200</v>
@@ -8461,97 +8656,100 @@
         <v>1200</v>
       </c>
       <c r="L81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M81" s="3">
         <v>2500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>600</v>
-      </c>
-      <c r="T81" s="3">
-        <v>700</v>
       </c>
       <c r="U81" s="3">
         <v>700</v>
       </c>
       <c r="V81" s="3">
+        <v>700</v>
+      </c>
+      <c r="W81" s="3">
         <v>800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6000</v>
-      </c>
-      <c r="AH81" s="3">
-        <v>700</v>
       </c>
       <c r="AI81" s="3">
         <v>700</v>
       </c>
       <c r="AJ81" s="3">
+        <v>700</v>
+      </c>
+      <c r="AK81" s="3">
         <v>-900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,8 +8791,9 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8634,8 +8833,8 @@
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -8712,8 +8911,11 @@
       <c r="AO83" s="3">
         <v>0</v>
       </c>
+      <c r="AP83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,41 +9521,44 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>-200</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>100</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>200</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1000</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
         <v>0</v>
       </c>
@@ -9361,73 +9578,76 @@
         <v>0</v>
       </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-8300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-9800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>9200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,8 +9689,9 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9510,8 +9731,8 @@
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -9588,8 +9809,11 @@
       <c r="AO91" s="3">
         <v>0</v>
       </c>
+      <c r="AP91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,31 +10053,34 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>4</v>
@@ -9867,8 +10097,8 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -9889,64 +10119,67 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>3000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>9800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>1000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,8 +10221,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10029,8 +10263,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10107,8 +10341,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,8 +10707,11 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10481,24 +10727,24 @@
       <c r="G100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
@@ -10511,8 +10757,8 @@
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
+      <c r="R100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
@@ -10583,8 +10829,11 @@
       <c r="AO100" s="3">
         <v>0</v>
       </c>
+      <c r="AP100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10624,8 +10873,8 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10702,8 +10951,11 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10711,17 +10963,17 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
@@ -10732,11 +10984,11 @@
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
@@ -10819,6 +11071,9 @@
         <v>0</v>
       </c>
       <c r="AO102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP102" s="3">
         <v>0</v>
       </c>
     </row>
